--- a/trig_final_ready_for_upload.xlsx
+++ b/trig_final_ready_for_upload.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P113"/>
+  <dimension ref="A1:P130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -533,7 +533,11 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>https://openstax.org/books/precalculus-2e/pages/7-2-sum-and-difference-identities</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -556,17 +560,17 @@
           <t>Using the formula for the cosine of the difference of two angles, find the exact value of $$cos(\frac{5π}{4}−\frac{π}{6}).$$</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>$$-\frac{\sqrt{6}+\sqrt{2}}{4}$$</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>\frac{-\sqrt{6}-\sqrt{2}}{4}</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
           <t>numeric</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
@@ -596,7 +600,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Recall that $$cos(A−B) = cos(A)cos(B) + sin(A)sin(B).$$</t>
+          <t>Recall that $$cos(A−B) = cos(A)cos(B) + sin(A)sin(B)$$</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -634,7 +638,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>In $$cos(\frac{5π}{4} − \frac{π}{6})$$, what are A and B?</t>
+          <t>In $$cos(\frac{5π}{4}−\frac{π}{6})$$, what are A and B?</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -644,7 +648,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>algebra</t>
+          <t>algebraic</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -684,7 +688,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Find the values of $$cos(A)$$, $$cos(B)$$, $$sin(A)$$, and $$sin(B).$$</t>
+          <t>Find the values of $$cos(A)$$, $$sin(A)$$, $$cos(B)$$, and $$sin(B)$$.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -721,12 +725,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Value of $$cos(A)$$</t>
+          <t>Value of cos(A)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>What is the exact value of $$cos(\frac{5π}{4})$$?</t>
+          <t>What is $$cos(\frac{5π}{4})$$?</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -771,17 +775,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Value of $$cos(B)$$</t>
+          <t>Value of sin(A)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>What is the exact value of $$cos(\frac{π}{6})$$?</t>
+          <t>What is $$sin(\frac{5π}{4})$$?</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>$$\frac{\sqrt{3}}{2}$$</t>
+          <t>$$-\frac{\sqrt{2}}{2}$$</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -821,17 +825,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Value of $$sin(A)$$</t>
+          <t>Value of cos(B)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>What is the exact value of $$sin(\frac{5π}{4})$$?</t>
+          <t>What is $$cos(\frac{π}{6})$$?</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>$$-\frac{\sqrt{2}}{2}$$</t>
+          <t>$$\frac{\sqrt{3}}{2}$$</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -871,12 +875,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Value of $$sin(B)$$</t>
+          <t>Value of sin(B)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>What is the exact value of $$sin(\frac{1}{2})$$?</t>
+          <t>What is $$sin(\frac{π}{6})$$?</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -963,22 +967,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Substitute into formula</t>
+          <t>Combine terms</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Substitute the values you found into $$cos(A)cos(B) + sin(A)sin(B).$$</t>
+          <t>Combine the terms to get the final exact value.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>$$(\frac{-\sqrt{2}}{2})(\frac{\sqrt{3}}{2}) + (\frac{-\sqrt{2}}{2})(\frac{1}{2})$$</t>
+          <t>$$-\frac{\sqrt{6}+\sqrt{2}}{4}$$</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>algebra</t>
+          <t>numeric</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1003,47 +1007,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>trig1</t>
+          <t>trig2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>problem</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Simplify</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Simplify the expression $$(\frac{-\sqrt{2}}{2})(\frac{\sqrt{3}}{2}) + (\frac{-\sqrt{2}}{2})(\frac{1}{2}).$$</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>$$\frac{-\sqrt{6}-\sqrt{2}}{4}$$</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>s7</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>h3</t>
-        </is>
-      </c>
+          <t>Finding the Exact Value Using the Formula for the Sum of Two Angles for Cosine</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>https://openstax.org/books/precalculus-2e/pages/7-2-sum-and-difference-identities</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -1058,16 +1046,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>problem</t>
+          <t>step</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Finding the Exact Value Using the Formula for the Sum of Two Angles for Cosine</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
+          <t>Find the exact value of $$cos(75^{∘}).$$</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>$$\frac{\sqrt{6}-\sqrt{2}}{4}$$</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
@@ -1088,26 +1084,26 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>step</t>
+          <t>hint</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Find the exact value of $$cos(75^{∘}).$$</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>\frac{\sqrt{6}-\sqrt{2}}{4}</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
+          <t>Choose appropriate angles</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Express $$75^{∘}$$ as a sum or difference of two common angles (e.g., $$30^{∘}, 45^{∘}, 60^{∘}, 90^{∘}$$).</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
@@ -1126,27 +1122,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>hint</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Decompose the angle</t>
+          <t>Break down the angle</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Express $$75^{∘}$$ as a sum of two special angles (e.g., $$30^{∘}, 45^{∘}, 60^{∘}$$).</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
+          <t>Which two common angles sum up to $$75^{∘}$$?</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>$$45^{∘}, 30^{∘}$$</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>algebraic</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
+          <t>s1</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
           <t>h1</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
@@ -1164,32 +1172,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>hint</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Identify angles</t>
+          <t>Apply the cosine sum formula</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Which two common angles (e.g., $$30^{∘}, 45^{∘}, 60^{∘}$$) add up to $$75^{∘}$$?</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>$$45^{∘} + 30^{∘}$$</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>algebra</t>
-        </is>
-      </c>
+          <t>Recall that $$cos(A+B) = cos(A)cos(B) - sin(A)sin(B)$$.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>s1</t>
+          <t>h2</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1214,29 +1214,37 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hint</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Applying the cosine sum formula</t>
+          <t>Identify A and B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Recall that $$cos(A+B) = cos(A)cos(B) - sin(A)sin(B).$$</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
+          <t>If $$75^{∘} = 45^{∘} + 30^{∘}$$, what are A and B?</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>$$A = 45^{∘}, B = 30^{∘}$$</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>algebraic</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr">
         <is>
+          <t>s2</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
           <t>h2</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>h1</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -1256,32 +1264,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>hint</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Identify A and B</t>
+          <t>Evaluate trigonometric values</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>If $$75^{∘} = 45^{∘} + 30^{∘}$$, what are A and B?</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>$$A = 45^{∘}, B = 30^{∘}$$</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>algebra</t>
-        </is>
-      </c>
+          <t>Find the values of $$cos(45^{∘})$$, $$sin(45^{∘})$$, $$cos(30^{∘})$$, and $$sin(30^{∘})$$.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>s2</t>
+          <t>h3</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1306,29 +1306,37 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>hint</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Evaluate trigonometric values</t>
+          <t>Value of cos(45°)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Find the values of $$cos(A)$$, $$cos(B)$$, $$sin(A)$$, and $$sin(B)$$ and substitute them into the formula.</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
+          <t>What is $$cos(45^{∘})$$?</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>$$\frac{\sqrt{2}}{2}$$</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
+          <t>s3</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
           <t>h3</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>h2</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -1353,12 +1361,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Value of $$cos(A)$$</t>
+          <t>Value of sin(45°)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>What is the exact value of $$cos(45^{∘})$$?</t>
+          <t>What is $$sin(45^{∘})$$?</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1373,7 +1381,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>s3</t>
+          <t>s4</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1403,12 +1411,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Value of $$cos(B)$$</t>
+          <t>Value of cos(30°)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>What is the exact value of $$cos(30^{∘})$$?</t>
+          <t>What is $$cos(30^{∘})$$?</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1423,7 +1431,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>s4</t>
+          <t>s5</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1453,17 +1461,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Value of $$sin(A)$$</t>
+          <t>Value of sin(30°)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>What is the exact value of $$sin(45^{∘})$$?</t>
+          <t>What is $$sin(30^{∘})$$?</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>$$\frac{\sqrt{2}}{2}$$</t>
+          <t>$$\frac{1}{2}$$</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1473,7 +1481,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>s5</t>
+          <t>s6</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1498,32 +1506,24 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>hint</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Value of $$sin(B)$$</t>
+          <t>Substitute and simplify</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>What is the exact value of $$sin(30^{∘})$$?</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>$$\frac{1}{2}$$</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
+          <t>Substitute the values into the formula and simplify the expression.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>s6</t>
+          <t>h4</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1553,12 +1553,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Substitute and simplify</t>
+          <t>Combine terms</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Substitute the values into $$cos(A)cos(B) - sin(A)sin(B)$$ and simplify.</t>
+          <t>Combine the terms to get the final exact value.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>h3</t>
+          <t>h4</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -1618,7 +1618,11 @@
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>https://openstax.org/books/precalculus-2e/pages/7-2-sum-and-difference-identities</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
@@ -1637,20 +1641,20 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Evaluate the expression $$sin(45^{∘}−30^{∘}).$$</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
+          <t>evaluate the expression $$sin(45^{∘}−30^{∘})$$</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>$$\frac{\sqrt{6}-\sqrt{2}}{4}$$</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>\frac{\sqrt{6}-\sqrt{2}}{4}</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
           <t>numeric</t>
         </is>
       </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
@@ -1675,12 +1679,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Applying the sine difference formula</t>
+          <t>Apply the sine difference formula</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Recall that $$sin(A−B) = sin(A)cos(B) - cos(A)sin(B).$$</t>
+          <t>Recall that $$sin(A−B) = sin(A)cos(B) - cos(A)sin(B)$$.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
@@ -1728,7 +1732,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>algebra</t>
+          <t>algebraic</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1768,7 +1772,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Find the values of $$sin(A)$$, $$cos(B)$$, $$cos(A)$$, and $$sin(B).$$</t>
+          <t>Find the values of $$sin(45^{∘})$$, $$cos(30^{∘})$$, $$cos(45^{∘})$$, and $$sin(30^{∘})$$.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
@@ -1805,12 +1809,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Value of $$sin(A)$$</t>
+          <t>Value of sin(45°)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>What is the exact value of $$sin(45^{∘})$$?</t>
+          <t>What is $$sin(45^{∘})$$?</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1855,12 +1859,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Value of $$cos(B)$$</t>
+          <t>Value of cos(30°)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>What is the exact value of $$cos(30^{∘})$$?</t>
+          <t>What is $$cos(30^{∘})$$?</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1905,12 +1909,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Value of $$cos(A)$$</t>
+          <t>Value of cos(45°)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>What is the exact value of $$cos(45^{∘})$$?</t>
+          <t>What is $$cos(45^{∘})$$?</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1955,12 +1959,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Value of $$sin(B)$$</t>
+          <t>Value of sin(30°)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>What is the exact value of $$sin(30^{∘})$$?</t>
+          <t>What is $$sin(30^{∘})$$?</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2047,22 +2051,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Substitute into formula</t>
+          <t>Combine terms</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Substitute the values you found into $$sin(A)cos(B) - cos(A)sin(B).$$</t>
+          <t>Combine the terms to get the final exact value.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>$$(\frac{\sqrt{2}}{2})(\frac{\sqrt{3}}{2}) - (\frac{\sqrt{2}}{2})(\frac{1}{2})$$</t>
+          <t>$$\frac{\sqrt{6}-\sqrt{2}}{4}$$</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>algebra</t>
+          <t>numeric</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2092,39 +2096,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>step</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Simplify</t>
+          <t>evaluate the expression $$sin(135^{∘}−120^{∘})$$</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Simplify the expression $$(\frac{\sqrt{2}}{2})(\frac{\sqrt{3}}{2}) - (\frac{\sqrt{2}}{2})(\frac{1}{2}).$$</t>
+          <t>$$\frac{\sqrt{6}-\sqrt{2}}{4}$$</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>$$\frac{\sqrt{6}-\sqrt{2}}{4}$$</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
           <t>numeric</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>s7</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>h3</t>
-        </is>
-      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
@@ -2142,26 +2134,26 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>step</t>
+          <t>hint</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Evaluate the expression $$sin(135^{∘}−120^{∘}).$$</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>\frac{\sqrt{6}-\sqrt{2}}{4}</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr"/>
+          <t>Apply the sine difference formula</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Recall that $$sin(A−B) = sin(A)cos(B) - cos(A)sin(B)$$.</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
@@ -2180,27 +2172,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>hint</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Applying the sine difference formula</t>
+          <t>Identify A and B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Recall that $$sin(A−B) = sin(A)cos(B) - cos(A)sin(B).$$</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+          <t>In $$sin(135^{∘}−120^{∘})$$, what are A and B?</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>$$A = 135^{∘}, B = 120^{∘}$$</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>algebraic</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
+          <t>s1</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
           <t>h1</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
@@ -2218,32 +2222,24 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>hint</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Identify A and B</t>
+          <t>Evaluate trigonometric values</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>In $$sin(135^{∘}−120^{∘})$$, what are A and B?</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>$$A = 135^{∘}, B = 120^{∘}$$</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>algebra</t>
-        </is>
-      </c>
+          <t>Find the values of $$sin(135^{∘})$$, $$cos(120^{∘})$$, $$cos(135^{∘})$$, and $$sin(120^{∘})$$.</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>s1</t>
+          <t>h2</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2268,29 +2264,37 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>hint</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Evaluate trigonometric values</t>
+          <t>Value of sin(135°)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Find the values of $$sin(A)$$, $$cos(B)$$, $$cos(A)$$, and $$sin(B).$$</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
+          <t>What is $$sin(135^{∘})$$?</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>$$\frac{\sqrt{2}}{2}$$</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr">
         <is>
+          <t>s2</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
           <t>h2</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>h1</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -2315,17 +2319,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Value of $$sin(A)$$</t>
+          <t>Value of cos(120°)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>What is the exact value of $$sin(135^{∘})$$?</t>
+          <t>What is $$cos(120^{∘})$$?</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>$$\frac{\sqrt{2}}{2}$$</t>
+          <t>$$-\frac{1}{2}$$</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2335,7 +2339,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>s2</t>
+          <t>s3</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2365,17 +2369,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Value of $$cos(B)$$</t>
+          <t>Value of cos(135°)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>What is the exact value of $$cos(120^{∘})$$?</t>
+          <t>What is $$cos(135^{∘})$$?</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>$$-\frac{1}{2}$$</t>
+          <t>$$-\frac{\sqrt{2}}{2}$$</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2385,7 +2389,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>s3</t>
+          <t>s4</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2415,17 +2419,17 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Value of $$cos(A)$$</t>
+          <t>Value of sin(120°)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>What is the exact value of $$cos(135^{∘})$$?</t>
+          <t>What is $$sin(120^{∘})$$?</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>$$-\frac{\sqrt{2}}{2}$$</t>
+          <t>$$\frac{\sqrt{3}}{2}$$</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2435,7 +2439,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>s4</t>
+          <t>s5</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2460,32 +2464,24 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>hint</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Value of $$sin(B)$$</t>
+          <t>Substitute and simplify</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>What is the exact value of $$sin(120^{∘})$$?</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>$$\frac{\sqrt{3}}{2}$$</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
+          <t>Substitute the values into the formula and simplify the expression.</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>s5</t>
+          <t>h3</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2510,29 +2506,37 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>hint</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Substitute and simplify</t>
+          <t>Combine terms</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Substitute the values into the formula and simplify the expression.</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
+          <t>Combine the terms to get the final exact value.</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>$$\frac{\sqrt{6}-\sqrt{2}}{4}$$</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
       <c r="G46" t="inlineStr">
         <is>
+          <t>s6</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
           <t>h3</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>h2</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -2547,48 +2551,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>trig3</t>
+          <t>trig4</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>problem</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Substitute into formula</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Substitute the values you found into $$sin(A)cos(B) - cos(A)sin(B).$$</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>$$(\frac{\sqrt{2}}{2})(-\frac{1}{2}) - (-\frac{\sqrt{2}}{2})(\frac{\sqrt{3}}{2})$$</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>algebra</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>s6</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>h3</t>
-        </is>
-      </c>
+          <t>Finding the Exact Value of an Expression Involving an Inverse Trigonometric Function</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>https://openstax.org/books/precalculus-2e/pages/7-2-sum-and-difference-identities</t>
+        </is>
+      </c>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
@@ -2597,44 +2585,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>trig3</t>
+          <t>trig4</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>step</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Simplify</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Simplify the expression $$(\frac{\sqrt{2}}{2})(-\frac{1}{2}) - (-\frac{\sqrt{2}}{2})(\frac{\sqrt{3}}{2}).$$</t>
-        </is>
-      </c>
+          <t>Find the exact value of $$sin(cos^{−1}\frac{1}{2}+sin^{−1}\frac{3}{5}).$$</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>$$\frac{-\sqrt{2}+\sqrt{6}}{4}$$</t>
+          <t xml:space="preserve">$$\frac{4\sqrt{3}+3}{10}$$ </t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>numeric</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>s7</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>h3</t>
-        </is>
-      </c>
+          <t>algebra</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
@@ -2652,18 +2628,26 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>problem</t>
+          <t>hint</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Finding the Exact Value of an Expression Involving an Inverse Trigonometric Function</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
+          <t>Apply the sine sum identity</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Recall the sum identity for sine: $$sin(A+B) = sinAcosB + cosAsinB$$</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
@@ -2682,27 +2666,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>step</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Find the exact value of $$sin(cos^{−1}\frac{1}{2}+sin^{−1}\frac{3}{5}).$$</t>
+          <t>Identify the identity</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>(4\sqrt{3}+3)/10</t>
+          <t>Which trigonometric identity is appropriate for $$sin(A+B)$$?</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
+          <t>$$sinAcosB + cosAsinB$$</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
           <t>algebra</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>s1</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
@@ -2725,22 +2721,26 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Applying the sine sum formula</t>
+          <t>Determine individual trigonometric values</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Recall that $$sin(A+B) = sinAcosB + cosAsinB$$</t>
+          <t>Find the values of $$sin(cos^{−1}\frac{1}{2})$$, $$cos(cos^{−1}\frac{1}{2})$$, $$sin(sin^{−1}\frac{3}{5})$$, and $$cos(sin^{−1}\frac{3}{5})$$.</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
+          <t>h2</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
           <t>h1</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
@@ -2763,17 +2763,17 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Identify A and B</t>
+          <t>Evaluate $$cos(cos^{−1}\frac{1}{2})$$</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>In the expression $$sin(cos^{−1}\frac{1}{2}+sin^{−1}\frac{3}{5})$$, what are A and B?</t>
+          <t>What is the value of $$cos(cos^{−1}\frac{1}{2})$$?</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">A = $$cos^{−1}\frac{1}{2}$$, B = $$sin^{−1}\frac{3}{5}$$ </t>
+          <t xml:space="preserve">$$\frac{1}{2}$$ </t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2783,12 +2783,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>s1</t>
+          <t>s2</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>h1</t>
+          <t>h2</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -2808,29 +2808,37 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>hint</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Evaluate inverse trigonometric functions</t>
+          <t>Evaluate $$sin(cos^{−1}\frac{1}{2})$$</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Determine the sine and cosine of A and B.</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
+          <t>If $$A = cos^{−1}\frac{1}{2}$$, what is $$sinA$$? (Hint: Draw a right triangle or use $$sin^2A + cos^2A = 1$$)</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$$\frac{\sqrt{3}}{2}$$ </t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>algebra</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr">
         <is>
+          <t>s3</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
           <t>h2</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>h1</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -2855,17 +2863,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Find sin A and cos A</t>
+          <t>Evaluate $$sin(sin^{−1}\frac{3}{5})$$</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>If $$A = cos^{−1}\frac{1}{2}$$, what are $$cosA$$ and $$sinA$$?</t>
+          <t>What is the value of $$sin(sin^{−1}\frac{3}{5})$$?</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">$$cosA = \frac{1}{2}$$, $$sinA = \frac{\sqrt{3}}{2}$$ </t>
+          <t xml:space="preserve">$$\frac{3}{5}$$ </t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2875,7 +2883,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>s2</t>
+          <t>s4</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2905,17 +2913,17 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Find sin B and cos B</t>
+          <t>Evaluate $$cos(sin^{−1}\frac{3}{5})$$</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>If $$B = sin^{−1}\frac{3}{5}$$, what are $$sinB$$ and $$cosB$$?</t>
+          <t>If $$B = sin^{−1}\frac{3}{5}$$, what is $$cosB$$? (Hint: Draw a right triangle or use $$sin^2B + cos^2B = 1$$)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">$$sinB = \frac{3}{5}$$, $$cosB = \frac{4}{5}$$ </t>
+          <t xml:space="preserve">$$\frac{4}{5}$$ </t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2925,7 +2933,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>s3</t>
+          <t>s5</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2943,38 +2951,14 @@
       <c r="P55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>trig4</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>hint</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Substitute and simplify</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Substitute the values into the sum formula and simplify.</t>
-        </is>
-      </c>
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>h3</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
@@ -2987,60 +2971,64 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>trig4</t>
+          <t>trig5</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>problem</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Substitute values</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Substitute the values into $$sinAcosB + cosAsinB$$.</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>$$(\frac{\sqrt{3}}{2})(\frac{4}{5}) + (\frac{1}{2})(\frac{3}{5})$$</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>algebra</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>s4</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>h3</t>
-        </is>
-      </c>
+          <t>Finding the Exact Value of an Expression Involving Tangent</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>https://openstax.org/books/precalculus-2e/pages/7-2-sum-and-difference-identities</t>
+        </is>
+      </c>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr"/>
-      <c r="B58" t="inlineStr"/>
-      <c r="C58" t="inlineStr"/>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>trig5</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>step</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Find the exact value of $$tan(\frac{π}{6}+\frac{π}{4}).$$</t>
+        </is>
+      </c>
       <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$$2+\sqrt{3}$$ </t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>algebra</t>
+        </is>
+      </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
@@ -3060,18 +3048,26 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>problem</t>
+          <t>hint</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Finding the Exact Value of an Expression Involving Tangent</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
+          <t>Apply the tangent sum identity</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Recall the sum identity for tangent: $$tan(A+B) = \frac{tanA + tanB}{1 - tanAtanB}$$</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
@@ -3090,27 +3086,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>step</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Find the exact value of $$tan(\frac{π}{6}+\frac{π}{4}).$$</t>
+          <t>Identify the identity</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">$$2+\sqrt{3}$$ </t>
+          <t>Which trigonometric identity is appropriate for $$tan(A+B)$$?</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
+          <t xml:space="preserve">$$\frac{tanA + tanB}{1 - tanAtanB}$$ </t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
           <t>algebra</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>s1</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
@@ -3133,22 +3141,26 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Applying the tangent sum formula</t>
+          <t>Recall special angle values</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Recall that $$tan(A+B) = \frac{tanA+tanB}{1-tanAtanB}$$</t>
+          <t>Determine the values of $$tan(\frac{π}{6})$$ and $$tan(\frac{π}{4})$$.</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
+          <t>h2</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
           <t>h1</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
@@ -3171,17 +3183,17 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Identify A and B</t>
+          <t>Evaluate $$tan(\frac{π}{6})$$</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>In the expression $$tan(\frac{π}{6}+\frac{π}{4})$$, what are A and B?</t>
+          <t>What is the exact value of $$tan(\frac{π}{6})$$?</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">A = $$\frac{π}{6}$$, B = $$\frac{π}{4}$$ </t>
+          <t xml:space="preserve">$$\frac{\sqrt{3}}{3}$$ </t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3191,12 +3203,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>s1</t>
+          <t>s2</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>h1</t>
+          <t>h2</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -3216,29 +3228,37 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>hint</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Evaluate tangent of angles</t>
+          <t>Evaluate $$tan(\frac{π}{4})$$</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Determine the tangent of A and B.</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
+          <t>What is the exact value of $$tan(\frac{π}{4})$$?</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>$$1$$</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>algebra</t>
+        </is>
+      </c>
       <c r="G63" t="inlineStr">
         <is>
+          <t>s3</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
           <t>h2</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>h1</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -3251,46 +3271,14 @@
       <c r="P63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>trig5</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>scaffold</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Find tan A</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>What is $$tan(\frac{π}{6})$$?</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">$$\frac{\sqrt{3}}{3}$$ </t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>algebra</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>s2</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" t="inlineStr"/>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
@@ -3303,27 +3291,23 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>trig5</t>
+          <t>trig6</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>step</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Find tan B</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>What is $$tan(\frac{π}{4})$$?</t>
-        </is>
-      </c>
+          <t>$$sin(α+β)$$</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">$$-\frac{63}{65}$$ </t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3331,16 +3315,8 @@
           <t>algebra</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>s3</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
@@ -3353,7 +3329,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>trig5</t>
+          <t>trig6</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3363,26 +3339,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Substitute and simplify</t>
+          <t>Recall the sine sum identity</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Substitute the values into the sum formula and simplify.</t>
+          <t>The identity for $$sin(α+β)$$ is $$sinαcosβ + cosαsinβ$$.</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>h3</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
+          <t>h1</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
@@ -3395,7 +3367,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>trig5</t>
+          <t>trig6</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3405,17 +3377,17 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Substitute values</t>
+          <t>Identify the identity</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Substitute the values into $$\frac{tanA+tanB}{1-tanAtanB}$$.</t>
+          <t>What is the formula for $$sin(α+β)$$?</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>$$\frac{\frac{\sqrt{3}}{3}+1}{1-(\frac{\sqrt{3}}{3})(1)}$$</t>
+          <t>$$sinαcosβ + cosαsinβ$$</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3425,12 +3397,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>s4</t>
+          <t>s1</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>h3</t>
+          <t>h1</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -3443,14 +3415,38 @@
       <c r="P67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr"/>
-      <c r="B68" t="inlineStr"/>
-      <c r="C68" t="inlineStr"/>
-      <c r="D68" t="inlineStr"/>
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>trig6</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>hint</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Determine missing trigonometric values</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Find $$cosα$$ and $$sinβ$$ using the given information and quadrant restrictions.</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
@@ -3468,23 +3464,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>problem</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Finding Multiple Sums and Differences of Angles</t>
+          <t>Find $$cosα$$</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Given $$sinα=\frac{3}{5},0&lt;α&lt;\frac{π}{2},cosβ=−\frac{5}{13},π&lt;β&lt;\frac{3π}{2},$$ find</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
+          <t>Given $$sinα=\frac{3}{5}$$ and $$0&lt;α&lt;\frac{π}{2}$$, what is $$cosα$$?</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$$\frac{4}{5}$$ </t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>algebra</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>s2</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
@@ -3502,27 +3514,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>step</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>$$sin(α+β)$$</t>
+          <t>Find $$sinβ$$</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>-63/65</t>
+          <t>Given $$cosβ=−\frac{5}{13}$$ and $$π&lt;β&lt;\frac{3π}{2}$$, what is $$sinβ$$?</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
+          <t xml:space="preserve">$$-\frac{12}{13}$$ </t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
           <t>algebra</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>s3</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
@@ -3540,26 +3564,26 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>hint</t>
+          <t>step</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Determine missing trigonometric values</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Use the given information and quadrant restrictions to find $$cosα$$ and $$sinβ$$.</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>h1</t>
-        </is>
-      </c>
+          <t>$$cos(α+β)$$</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$$\frac{16}{65}$$ </t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>algebra</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
@@ -3578,39 +3602,27 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>hint</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Find $$cosα$$</t>
+          <t>Recall the cosine sum identity</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Given $$sinα=\frac{3}{5}$$ and $$0&lt;α&lt;\frac{π}{2}$$, what is $$cosα$$?</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>4/5</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>algebra</t>
-        </is>
-      </c>
+          <t>The identity for $$cos(α+β)$$ is $$cosαcosβ - sinαsinβ$$.</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>s1</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
           <t>h1</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
@@ -3633,17 +3645,17 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Find $$sinβ$$</t>
+          <t>Identify the identity</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Given $$cosβ=−\frac{5}{13}$$ and $$π&lt;β&lt;\frac{3π}{2}$$, what is $$sinβ$$?</t>
+          <t>What is the formula for $$cos(α+β)$$?</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>-12/13</t>
+          <t>$$cosαcosβ - sinαsinβ$$</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3653,7 +3665,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>s2</t>
+          <t>s1</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3683,12 +3695,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Apply the sine sum formula</t>
+          <t>Use previously found values</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Recall that $$sin(α+β) = sinαcosβ + cosαsinβ$$</t>
+          <t>Use the values of $$sinα, cosα, sinβ, cosβ$$ determined earlier.</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
@@ -3725,17 +3737,17 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Substitute and calculate</t>
+          <t>What is $$sinα$$?</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Substitute the values into the formula and simplify.</t>
+          <t>What is the value of $$sinα$$?</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>$$(\frac{3}{5})(-\frac{5}{13}) + (\frac{4}{5})(-\frac{12}{13})$$</t>
+          <t xml:space="preserve">$$\frac{3}{5}$$ </t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3745,7 +3757,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>s3</t>
+          <t>s2</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3770,27 +3782,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>step</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>$$cos(α+β)$$</t>
+          <t>What is $$cosα$$?</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>16/65</t>
+          <t>What is the value of $$cosα$$?</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
+          <t xml:space="preserve">$$\frac{4}{5}$$ </t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
           <t>algebra</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>s3</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
@@ -3808,27 +3832,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>hint</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Apply the cosine sum formula</t>
+          <t>What is $$sinβ$$?</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Recall that $$cos(α+β) = cosαcosβ - sinαsinβ$$</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
+          <t>What is the value of $$sinβ$$?</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$$-\frac{12}{13}$$ </t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>algebra</t>
+        </is>
+      </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>h1</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr"/>
+          <t>s4</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
@@ -3851,17 +3887,17 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Substitute and calculate</t>
+          <t>What is $$cosβ$$?</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Substitute the previously found values into the formula and simplify.</t>
+          <t>What is the value of $$cosβ$$?</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>$$(\frac{4}{5})(-\frac{5}{13}) - (\frac{3}{5})(-\frac{12}{13})$$</t>
+          <t xml:space="preserve">$$-\frac{5}{13}$$ </t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3871,12 +3907,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>s1</t>
+          <t>s5</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>h1</t>
+          <t>h2</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -3904,17 +3940,17 @@
           <t>$$tan(α+β)$$</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>-63/16</t>
-        </is>
-      </c>
+      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
+          <t xml:space="preserve">$$-\frac{63}{16}$$ </t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
           <t>algebra</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
@@ -3939,12 +3975,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Determine tangent values</t>
+          <t>Recall the tangent sum identity</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Use the previously found sine and cosine values to find $$tanα$$ and $$tanβ$$.</t>
+          <t>The identity for $$tan(α+β)$$ is $$\frac{tanα + tanβ}{1 - tanαtanβ}$$. Alternatively, you can use $$\frac{sin(α+β)}{cos(α+β)}$$.</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
@@ -3977,17 +4013,17 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Find $$tanα$$</t>
+          <t>Identify the identity</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>What is $$tanα$$?</t>
+          <t>What is the formula for $$tan(α+β)$$?</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t xml:space="preserve">$$\frac{tanα + tanβ}{1 - tanαtanβ}$$ </t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -4022,32 +4058,24 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>hint</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Find $$tanβ$$</t>
+          <t>Determine $$tanα$$ and $$tanβ$$</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>What is $$tanβ$$?</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>12/5</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>algebra</t>
-        </is>
-      </c>
+          <t>Find $$tanα$$ and $$tanβ$$ using the given information and quadrant restrictions.</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>s2</t>
+          <t>h2</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4072,29 +4100,37 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>hint</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Apply the tangent sum formula</t>
+          <t>Find $$tanα$$</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Recall that $$tan(α+β) = \frac{tanα+tanβ}{1-tanαtanβ}$$</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
+          <t>Given $$sinα=\frac{3}{5}$$ and $$cosα=\frac{4}{5}$$, what is $$tanα$$?</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$$\frac{3}{4}$$ </t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>algebra</t>
+        </is>
+      </c>
       <c r="G83" t="inlineStr">
         <is>
+          <t>s2</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
           <t>h2</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>h1</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -4119,17 +4155,17 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Substitute and calculate</t>
+          <t>Find $$tanβ$$</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Substitute the values into the formula and simplify.</t>
+          <t>Given $$sinβ=-\frac{12}{13}$$ and $$cosβ=-\frac{5}{13}$$, what is $$tanβ$$?</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>$$\frac{\frac{3}{4}+\frac{12}{5}}{1-(\frac{3}{4})(\frac{12}{5})}$$</t>
+          <t xml:space="preserve">$$\frac{12}{5}$$ </t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -4172,17 +4208,17 @@
           <t>$$tan(α−β)$$</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>-33/56</t>
-        </is>
-      </c>
+      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
+          <t xml:space="preserve">$$-\frac{33}{56}$$ </t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
           <t>algebra</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
@@ -4207,12 +4243,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Apply the tangent difference formula</t>
+          <t>Recall the tangent difference identity</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Recall that $$tan(α−β) = \frac{tanα-tanβ}{1+tanαtanβ}$$</t>
+          <t>The identity for $$tan(α−β)$$ is $$\frac{tanα - tanβ}{1 + tanαtanβ}$$.</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -4245,17 +4281,17 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Substitute and calculate</t>
+          <t>Identify the identity</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Substitute the previously found tangent values into the formula and simplify.</t>
+          <t>What is the formula for $$tan(α−β)$$?</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>$$\frac{\frac{3}{4}-\frac{12}{5}}{1+(\frac{3}{4})(\frac{12}{5})}$$</t>
+          <t xml:space="preserve">$$\frac{tanα - tanβ}{1 + tanαtanβ}$$ </t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -4283,14 +4319,38 @@
       <c r="P87" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr"/>
-      <c r="B88" t="inlineStr"/>
-      <c r="C88" t="inlineStr"/>
-      <c r="D88" t="inlineStr"/>
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>trig6</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>hint</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Use previously found tangent values</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Use the values of $$tanα$$ and $$tanβ$$ determined earlier.</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
@@ -4303,24 +4363,44 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>trig7</t>
+          <t>trig6</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>problem</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Finding a Cofunction with the Same Value as the Given Expression</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
+          <t>What is $$tanα$$?</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>What is the value of $$tanα$$?</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$$\frac{3}{4}$$ </t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>algebra</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>s2</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
@@ -4333,23 +4413,27 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>trig7</t>
+          <t>trig6</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>step</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Write $$tan\frac{π}{9}$$ in terms of its cofunction.</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr"/>
+          <t>What is $$tanβ$$?</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>What is the value of $$tanβ$$?</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>$$cot\frac{7π}{18}$$</t>
+          <t xml:space="preserve">$$\frac{12}{5}$$ </t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4357,8 +4441,16 @@
           <t>algebra</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>s3</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
@@ -4376,43 +4468,59 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>hint</t>
+          <t>problem</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Recall cofunction identities</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Recall that $$tan(θ) = cot(\frac{π}{2} - θ).$$</t>
-        </is>
-      </c>
+          <t>Finding a Cofunction with the Same Value as the Given Expression</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>h1</t>
-        </is>
-      </c>
+      <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>https://openstax.org/books/precalculus-2e/pages/7-2-sum-and-difference-identities</t>
+        </is>
+      </c>
       <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr"/>
       <c r="P91" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr"/>
-      <c r="B92" t="inlineStr"/>
-      <c r="C92" t="inlineStr"/>
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>trig7</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>step</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Write $$tan\frac{π}{9}$$ in terms of its cofunction.</t>
+        </is>
+      </c>
       <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>$$cot\frac{7π}{18}$$</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>algebra</t>
+        </is>
+      </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr"/>
@@ -4427,31 +4535,31 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>trig8</t>
+          <t>trig7</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>step</t>
+          <t>hint</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Evaluate the expression $$sin(α+β)+sin(α−β).$$</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>$$2sinαcosβ$$</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>algebra</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr"/>
+          <t>Recall Cofunction Identities</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remember the cofunction identities relating tangent and cotangent: `tan(θ) = cot(π/2 - θ)`. </t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
@@ -4465,32 +4573,44 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>trig8</t>
+          <t>trig7</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>hint</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Recall sum and difference identities for sine</t>
+          <t>Identify θ</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Recall the sum and difference formulas for sine: $$sin(A+B) = sinAcosB + cosAsinB$$ and $$sin(A-B) = sinAcosB - cosAsinB$$.</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
+          <t>In `tan(π/9)`, what is the value of θ?</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>$$\frac{π}{9}$$</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>algebra</t>
+        </is>
+      </c>
       <c r="G94" t="inlineStr">
         <is>
+          <t>s1</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
           <t>h1</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
@@ -4501,14 +4621,38 @@
       <c r="P94" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr"/>
-      <c r="B95" t="inlineStr"/>
-      <c r="C95" t="inlineStr"/>
-      <c r="D95" t="inlineStr"/>
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>trig7</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>hint</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Apply the Identity</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Substitute θ into the cofunction identity `cot(π/2 - θ)`. </t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
@@ -4521,23 +4665,27 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>trig9</t>
+          <t>trig7</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>step</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Evaluate the expression $$\frac{sin(α−β)}{cosαcosβ}.$$</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr"/>
+          <t>Calculate the Angle</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>What is `π/2 - π/9`?</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>$$tanα−tanβ$$</t>
+          <t>$$\frac{7π}{18}$$</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -4545,8 +4693,16 @@
           <t>algebra</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>s2</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
@@ -4559,36 +4715,32 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>trig9</t>
+          <t>trig8</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>hint</t>
+          <t>problem</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Recall the sine difference identity</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Recall the difference formula for sine: $$sin(A-B) = sinAcosB - cosAsinB$$.</t>
-        </is>
-      </c>
+          <t>Verifying an Identity Involving Sine</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>h1</t>
-        </is>
-      </c>
+      <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>https://openstax.org/books/precalculus-2e/pages/7-2-sum-and-difference-identities</t>
+        </is>
+      </c>
       <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr"/>
@@ -4597,37 +4749,37 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>trig10</t>
+          <t>trig8</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>problem</t>
+          <t>step</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Using Sum and Difference Formulas to Solve an Application Problem</t>
+          <t>Evaluate the expression $$sin(α+β)+sin(α−β)$$</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>$$2sinαcosβ$$</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>algebra</t>
+        </is>
+      </c>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>https://openstax.org/books/precalculus-2e/pages/7-3-sum-and-difference-formulas</t>
-        </is>
-      </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>Using Sum and Difference Formulas to Solve an Application Problem</t>
-        </is>
-      </c>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr"/>
       <c r="O98" t="inlineStr"/>
       <c r="P98" t="inlineStr"/>
@@ -4635,31 +4787,31 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>trig10</t>
+          <t>trig8</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>step</t>
+          <t>hint</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Evaluate the expression for $$tanθ$$ given $$m_1$$ and $$m_2$$ are slopes of lines $$L_1$$ and $$L_2$$ respectively, and $$θ$$ is the acute angle between them.</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>\frac{m_{2}−m_{1}}{1+m_{1}m_{2}}</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>algebraic</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr"/>
+          <t>Recall Sum and Difference Identities for Sine</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Remember the sum and difference identities for sine: `sin(A+B) = sinAcosB + cosAsinB` and `sin(A-B) = sinAcosB - cosAsinB`.</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr"/>
@@ -4673,32 +4825,44 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>trig10</t>
+          <t>trig8</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>hint</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Relating angles and slopes</t>
+          <t>Expand sin(α+β)</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Recall that the angle a line makes with the positive x-axis is related to its slope by $$tanθ = m$$.</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
+          <t>Using the sum identity, what is `sin(α+β)`?</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>$$sinαcosβ + cosαsinβ$$</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>algebra</t>
+        </is>
+      </c>
       <c r="G100" t="inlineStr">
         <is>
+          <t>s1</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
           <t>h1</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
@@ -4711,37 +4875,29 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>trig10</t>
+          <t>trig8</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>hint</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Identify the angles</t>
+          <t>Expand sin(α-β)</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Let $$θ_1$$ and $$θ_2$$ be the angles $$L_1$$ and $$L_2$$ make with the positive x-axis. How is $$θ$$ related to $$θ_1$$ and $$θ_2$$?</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>θ = θ_2 - θ_1</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>algebraic</t>
-        </is>
-      </c>
+          <t>Using the difference identity, what is `sin(α-β)`?</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>s1</t>
+          <t>h2</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4761,34 +4917,42 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>trig10</t>
+          <t>trig8</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>hint</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Tangent difference formula</t>
+          <t>Expand sin(α-β)</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Recall the tangent difference formula: $$tan(A-B) = \frac{tanA - tanB}{1 + tanA tanB}$$.</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr"/>
+          <t>What is `sin(α-β)`?</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>$$sinαcosβ - cosαsinβ$$</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>algebra</t>
+        </is>
+      </c>
       <c r="G102" t="inlineStr">
         <is>
+          <t>s2</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
           <t>h2</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>h1</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -4803,42 +4967,34 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>trig10</t>
+          <t>trig8</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>hint</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Apply the formula</t>
+          <t>Combine the Expanded Forms</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Substitute $$θ_1$$ and $$θ_2$$ into the tangent difference formula.</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>tan(θ_2 - θ_1) = \frac{tanθ_2 - tanθ_1}{1 + tanθ_2 tanθ_1}</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>algebraic</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Add the expanded forms of `sin(α+β)` and `sin(α-β)`. </t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>s2</t>
+          <t>h3</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>h2</t>
+          <t>h1,h2</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -4853,34 +5009,42 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>trig10</t>
+          <t>trig8</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>hint</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Substitute slopes</t>
+          <t>Simplify the Sum</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Use the fact that $$tanθ_1 = m_1$$ and $$tanθ_2 = m_2$$.</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr"/>
+          <t>What do you get when you add `(sinαcosβ + cosαsinβ)` and `(sinαcosβ - cosαsinβ)`?</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>$$2sinαcosβ$$</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>algebra</t>
+        </is>
+      </c>
       <c r="G104" t="inlineStr">
         <is>
+          <t>s3</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
           <t>h3</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>h2</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -4895,48 +5059,32 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>trig10</t>
+          <t>trig9</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>problem</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Final substitution</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>Substitute $$m_1$$ and $$m_2$$ into the expression from the previous step.</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>\frac{m_{2}−m_{1}}{1+m_{1}m_{2}}</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>algebraic</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>s3</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>h3</t>
-        </is>
-      </c>
+          <t>Verifying an Identity Involving Tangent</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>https://openstax.org/books/precalculus-2e/pages/7-2-sum-and-difference-identities</t>
+        </is>
+      </c>
       <c r="M105" t="inlineStr"/>
       <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr"/>
@@ -4945,37 +5093,37 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>trig11</t>
+          <t>trig9</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>problem</t>
+          <t>step</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Investigating a Guy-wire Problem</t>
+          <t>Evaluate the expression $$\frac{sin(α−β)}{cosαcosβ}$$</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>$$tanα−tanβ$$</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>algebra</t>
+        </is>
+      </c>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr">
-        <is>
-          <t>https://openstax.org/books/precalculus-2e/pages/7-3-sum-and-difference-formulas</t>
-        </is>
-      </c>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>Using Sum and Difference Formulas to Solve an Application Problem</t>
-        </is>
-      </c>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
       <c r="O106" t="inlineStr"/>
       <c r="P106" t="inlineStr"/>
@@ -4983,31 +5131,31 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>trig11</t>
+          <t>trig9</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>step</t>
+          <t>hint</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Find the angle $$α$$ between the two guy-wires.</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr"/>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>arctan(\frac{35}{438})</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr"/>
+          <t>Recall Difference Identity for Sine</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Remember the difference identity for sine: `sin(A-B) = sinAcosB - cosAsinB`.</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
       <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr"/>
@@ -5021,32 +5169,44 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>trig11</t>
+          <t>trig9</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>hint</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Identify relevant triangles</t>
+          <t>Expand sin(α-β)</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Consider the two right triangles formed by each wire, the pole, and the ground. What are the angles these wires make with the ground?</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr"/>
+          <t>Using the difference identity, what is `sin(α-β)`?</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>$$sinαcosβ - cosαsinβ$$</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>algebra</t>
+        </is>
+      </c>
       <c r="G108" t="inlineStr">
         <is>
+          <t>s1</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
           <t>h1</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
@@ -5059,37 +5219,29 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>trig11</t>
+          <t>trig9</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>hint</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Calculate angles with ground</t>
+          <t>Substitute and Separate</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Let $$θ_R$$ be the angle wire R makes with the ground and $$θ_S$$ be the angle wire S makes with the ground. What are $$tan(θ_R)$$ and $$tan(θ_S)$$?</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>tan(θ_R) = 47/50, tan(θ_S) = 40/50</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>algebraic</t>
-        </is>
-      </c>
+          <t>Substitute the expanded form of `sin(α-β)` into the numerator and then separate the fraction into two terms.</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>s1</t>
+          <t>h2</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -5109,34 +5261,42 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>trig11</t>
+          <t>trig9</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>hint</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Relate angles</t>
+          <t>Separate the Fraction</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>The angle $$α$$ between the wires at the ground attachment point is the difference between the angles each wire makes with the ground.</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr"/>
+          <t>After substituting, how can you rewrite `$$\frac{sinαcosβ - cosαsinβ}{cosαcosβ}$$` as two separate fractions?</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>$$\frac{sinαcosβ}{cosαcosβ} - \frac{cosαsinβ}{cosαcosβ}$$</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>algebra</t>
+        </is>
+      </c>
       <c r="G110" t="inlineStr">
         <is>
+          <t>s2</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
           <t>h2</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>h1</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -5151,37 +5311,29 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>trig11</t>
+          <t>trig9</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>hint</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Express $$α$$</t>
+          <t>Simplify Each Term</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Write $$α$$ in terms of $$θ_R$$ and $$θ_S$$.</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>α = θ_R - θ_S</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>algebraic</t>
-        </is>
-      </c>
+          <t>Simplify each of the two fractions using the definitions of tangent (`tanθ = sinθ/cosθ`).</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>s2</t>
+          <t>h3</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -5201,34 +5353,42 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>trig11</t>
+          <t>trig9</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>hint</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Tangent difference formula</t>
+          <t>Simplify the First Term</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Use the tangent difference formula: $$tan(A-B) = \frac{tanA - tanB}{1 + tanA tanB}$$.</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr"/>
+          <t>What does `$$\frac{sinαcosβ}{cosαcosβ}$$` simplify to?</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>$$tanα$$</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>algebra</t>
+        </is>
+      </c>
       <c r="G112" t="inlineStr">
         <is>
+          <t>s3</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
           <t>h3</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>h2</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -5243,7 +5403,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>trig11</t>
+          <t>trig9</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -5253,27 +5413,27 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Apply formula and solve</t>
+          <t>Simplify the Second Term</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Substitute the tangent values and solve for $$α$$.</t>
+          <t>What does `$$\frac{cosαsinβ}{cosαcosβ}$$` simplify to?</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>arctan(\frac{35}{438})</t>
+          <t>$$tanβ$$</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>numeric</t>
+          <t>algebra</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>s3</t>
+          <t>s4</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -5290,6 +5450,712 @@
       <c r="O113" t="inlineStr"/>
       <c r="P113" t="inlineStr"/>
     </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>trig10</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>problem</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Using Sum and Difference Formulas to Solve an Application Problem</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>https://openstax.org/books/precalculus-2e/pages/7-2-sum-and-difference-identities</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
+      <c r="O114" t="inlineStr"/>
+      <c r="P114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>trig10</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>step</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Derive the formula for the tangent of the acute angle between two lines, $$L_1$$ and $$L_2$$, with slopes $$m_1$$ and $$m_2$$ respectively.</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>$$\frac{m_{2}−m_{1}}{1+m_{1}m_{2}}$$</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>algebraic</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
+      <c r="O115" t="inlineStr"/>
+      <c r="P115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>trig10</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>hint</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Relate slopes to angles</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Recall that the slope of a line is equal to the tangent of the angle the line makes with the positive x-axis.</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
+      <c r="O116" t="inlineStr"/>
+      <c r="P116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>trig10</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>scaffold</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Identify $$tan\theta_1$$ and $$tan\theta_2$$</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>If $$\theta_1$$ is the angle $$L_1$$ makes with the x-axis and $$\theta_2$$ for $$L_2$$, what are $$tan\theta_1$$ and $$tan\theta_2$$ in terms of $$m_1$$ and $$m_2$$?</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>$$tan\theta_1 = m_1, tan\theta_2 = m_2$$</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>algebraic</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>s1</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
+      <c r="O117" t="inlineStr"/>
+      <c r="P117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>trig10</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>hint</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Angle relationship</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>The angle $$\theta$$ between the lines can be expressed as the difference between the angles $$\theta_1$$ and $$\theta_2$$.</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
+      <c r="O118" t="inlineStr"/>
+      <c r="P118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>trig10</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>scaffold</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Express $$\theta$$</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>How can you express $$\theta$$ using $$\theta_1$$ and $$\theta_2$$?</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>$$\theta = \theta_2 - \theta_1$$</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>algebraic</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>s2</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
+      <c r="O119" t="inlineStr"/>
+      <c r="P119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>trig10</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>hint</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Tangent difference formula</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Apply the tangent difference identity: $$tan(A - B) = \frac{tan A - tan B}{1 + tan A tan B}$$.</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>h3</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
+      <c r="O120" t="inlineStr"/>
+      <c r="P120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>trig10</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>scaffold</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Apply tangent difference</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Substitute $$tan\theta_1 = m_1$$ and $$tan\theta_2 = m_2$$ into the tangent difference formula for $$tan(\theta_2 - \theta_1)$$.</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>$$\frac{m_{2}−m_{1}}{1+m_{1}m_{2}}$$</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>algebraic</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>s3</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>h3</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
+      <c r="O121" t="inlineStr"/>
+      <c r="P121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr"/>
+      <c r="B122" t="inlineStr"/>
+      <c r="C122" t="inlineStr"/>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
+      <c r="O122" t="inlineStr"/>
+      <c r="P122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>trig11</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>problem</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Investigating a Guy-wire Problem</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>https://openstax.org/books/precalculus-2e/pages/7-2-sum-and-difference-identities</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
+      <c r="O123" t="inlineStr"/>
+      <c r="P123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>trig11</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>step</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Find the angle $$α$$ between the two guy-wires attached to a pole at heights 47 feet and 40 feet, both attached to the ground 50 feet from the pole.</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>$$\arctan\left(\frac{35}{438}\right)$$</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
+      <c r="O124" t="inlineStr"/>
+      <c r="P124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>trig11</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>hint</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Identify angles of elevation</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Consider the angles of elevation that each wire makes with the ground. Let these be $$\theta_R$$ for wire R and $$\theta_S$$ for wire S.</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
+      <c r="O125" t="inlineStr"/>
+      <c r="P125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>trig11</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>scaffold</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Calculate $$tan(\theta_R)$$ and $$tan(\theta_S)$$</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>What are the tangent values for the angles of elevation of wire R (47 ft high) and wire S (40 ft high), given they are both 50 ft from the pole?</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>$$tan(\theta_R) = 47/50, tan(\theta_S) = 40/50$$</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>algebraic</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>s1</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
+      <c r="O126" t="inlineStr"/>
+      <c r="P126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>trig11</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>hint</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Angle between wires</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>The angle $$\alpha$$ between the wires at the ground attachment point is the difference between their angles of elevation.</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
+      <c r="O127" t="inlineStr"/>
+      <c r="P127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>trig11</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>scaffold</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Express $$\alpha$$</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>How can you express $$\alpha$$ in terms of $$\theta_R$$ and $$\theta_S$$?</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>$$\alpha = \theta_R - \theta_S$$</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>algebraic</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>s2</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
+      <c r="O128" t="inlineStr"/>
+      <c r="P128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>trig11</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>hint</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Tangent difference formula</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Apply the tangent difference identity: $$tan(A - B) = \frac{tan A - tan B}{1 + tan A tan B}$$ to find $$tan(\alpha)$$.</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>h3</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
+      <c r="O129" t="inlineStr"/>
+      <c r="P129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>trig11</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>scaffold</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Calculate $$tan(\alpha)$$</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Substitute the tangent values from Scaffold 1 into the tangent difference formula to find $$tan(\alpha)$$.</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>35/438</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>s3</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>h3</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
+      <c r="O130" t="inlineStr"/>
+      <c r="P130" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trig_final_ready_for_upload.xlsx
+++ b/trig_final_ready_for_upload.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P130"/>
+  <dimension ref="A1:P101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -533,12 +533,12 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
         <is>
           <t>https://openstax.org/books/precalculus-2e/pages/7-2-sum-and-difference-identities</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -557,20 +557,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Using the formula for the cosine of the difference of two angles, find the exact value of $$cos(\frac{5π}{4}−\frac{π}{6}).$$</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+          <t>Evaluate the expression $$cos(\frac{5π}{4}−\frac{π}{6}).$$</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
         <is>
           <t>$$-\frac{\sqrt{6}+\sqrt{2}}{4}$$</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>numeric</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
@@ -600,7 +600,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Recall that $$cos(A−B) = cos(A)cos(B) + sin(A)sin(B)$$</t>
+          <t>Recall that $cos(A−B) = cos(A)cos(B) + sin(A)sin(B)$.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -638,17 +638,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>In $$cos(\frac{5π}{4}−\frac{π}{6})$$, what are A and B?</t>
+          <t>In $cos(\frac{5π}{4}−\frac{π}{6})$, what are A and B?</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>$$A = \frac{5π}{4}, B = \frac{π}{6}$$</t>
+          <t>$$A=\frac{5π}{4}, B=\frac{π}{6}$$</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>algebraic</t>
+          <t>algebra</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Find the values of $$cos(A)$$, $$sin(A)$$, $$cos(B)$$, and $$sin(B)$$.</t>
+          <t>Determine the sine and cosine values for $A=\frac{5π}{4}$ and $B=\frac{π}{6}$.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -698,11 +698,7 @@
           <t>h2</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>h1</t>
-        </is>
-      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -725,12 +721,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Value of cos(A)</t>
+          <t>Find $cos(A)$</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>What is $$cos(\frac{5π}{4})$$?</t>
+          <t>What is the exact value of $cos(\frac{5π}{4})$?</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -770,39 +766,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>hint</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Value of sin(A)</t>
+          <t>Substitute and simplify</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>What is $$sin(\frac{5π}{4})$$?</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>$$-\frac{\sqrt{2}}{2}$$</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
+          <t>Substitute the values into the formula and simplify the expression.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>s3</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
+          <t>h3</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -825,32 +809,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Value of cos(B)</t>
+          <t>Substitute values</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>What is $$cos(\frac{π}{6})$$?</t>
+          <t>Substitute the values of $cos(A)$, $cos(B)$, $sin(A)$, and $sin(B)$ into the formula. What is the resulting expression before simplification?</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>$$\frac{\sqrt{3}}{2}$$</t>
+          <t>$$(-\frac{\sqrt{2}}{2})(\frac{\sqrt{3}}{2}) + (-\frac{\sqrt{2}}{2})(\frac{1}{2})$$</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>numeric</t>
+          <t>algebra</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>s4</t>
+          <t>s3</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>h2</t>
+          <t>h3</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -863,46 +847,14 @@
       <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>trig1</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>scaffold</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Value of sin(B)</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>What is $$sin(\frac{π}{6})$$?</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>$$\frac{1}{2}$$</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>s5</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
@@ -915,40 +867,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>trig1</t>
+          <t>trig2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>hint</t>
+          <t>problem</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Substitute and simplify</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Substitute the values into the formula and simplify the expression.</t>
-        </is>
-      </c>
+          <t>Finding the Exact Value Using the Formula for the Sum of Two Angles for Cosine</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>h3</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://openstax.org/books/precalculus-2e/pages/7-2-sum-and-difference-identities</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -957,27 +901,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>trig1</t>
+          <t>trig2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>step</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Combine terms</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Combine the terms to get the final exact value.</t>
-        </is>
-      </c>
+          <t>Find the exact value of $$cos(75^{∘}).$$</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>$$-\frac{\sqrt{6}+\sqrt{2}}{4}$$</t>
+          <t>$$\frac{\sqrt{6}-\sqrt{2}}{4}$$</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -985,16 +925,8 @@
           <t>numeric</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>s6</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>h3</t>
-        </is>
-      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
@@ -1012,26 +944,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>problem</t>
+          <t>hint</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Finding the Exact Value Using the Formula for the Sum of Two Angles for Cosine</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
+          <t>Express angle as a sum</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>How can $75^\circ$ be written as a sum of two common angles (e.g., $30^\circ, 45^\circ, 60^\circ$)?</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>$$45^\circ + 30^\circ$$</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>algebra</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>https://openstax.org/books/precalculus-2e/pages/7-2-sum-and-difference-identities</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -1046,27 +990,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>step</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Find the exact value of $$cos(75^{∘}).$$</t>
+          <t>Identify A and B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>$$\frac{\sqrt{6}-\sqrt{2}}{4}$$</t>
+          <t>What are A and B if $75^\circ = A+B$ using common angles?</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>numeric</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+          <t>$$A=45^\circ, B=30^\circ$$</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>algebra</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>s1</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
@@ -1089,19 +1045,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Choose appropriate angles</t>
+          <t>Recall the cosine sum formula</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Express $$75^{∘}$$ as a sum or difference of two common angles (e.g., $$30^{∘}, 45^{∘}, 60^{∘}, 90^{∘}$$).</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
+          <t>What is the formula for $cos(A+B)$?</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>$$cos(A)cos(B) - sin(A)sin(B)$$</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>algebra</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>h1</t>
+          <t>h2</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -1127,32 +1091,32 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Break down the angle</t>
+          <t>Apply the formula</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Which two common angles sum up to $$75^{∘}$$?</t>
+          <t>What is $cos(45^\circ + 30^\circ)$ in terms of $cos(45^\circ)$, $cos(30^\circ)$, $sin(45^\circ)$, and $sin(30^\circ)$?</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>$$45^{∘}, 30^{∘}$$</t>
+          <t>$$cos(45^\circ)cos(30^\circ) - sin(45^\circ)sin(30^\circ)$$</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>algebraic</t>
+          <t>algebra</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>s1</t>
+          <t>s2</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>h1</t>
+          <t>h2</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -1177,26 +1141,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Apply the cosine sum formula</t>
+          <t>Evaluate trigonometric values</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Recall that $$cos(A+B) = cos(A)cos(B) - sin(A)sin(B)$$.</t>
+          <t>Determine the sine and cosine values for $A=45^\circ$ and $B=30^\circ$.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>h2</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>h1</t>
-        </is>
-      </c>
+          <t>h3</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
@@ -1219,32 +1179,32 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Identify A and B</t>
+          <t>Find $cos(45^\circ)$</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>If $$75^{∘} = 45^{∘} + 30^{∘}$$, what are A and B?</t>
+          <t>What is the exact value of $cos(45^\circ)$?</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>$$A = 45^{∘}, B = 30^{∘}$$</t>
+          <t>$$\frac{\sqrt{2}}{2}$$</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>algebraic</t>
+          <t>numeric</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>s2</t>
+          <t>s3</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>h2</t>
+          <t>h3</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -1257,38 +1217,14 @@
       <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>trig2</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>hint</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Evaluate trigonometric values</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Find the values of $$cos(45^{∘})$$, $$sin(45^{∘})$$, $$cos(30^{∘})$$, and $$sin(30^{∘})$$.</t>
-        </is>
-      </c>
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>h3</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
@@ -1301,27 +1237,23 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>trig2</t>
+          <t>trig3</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>step</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Value of cos(45°)</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>What is $$cos(45^{∘})$$?</t>
-        </is>
-      </c>
+          <t>Evaluate the expression $$sin(45^{∘}−30^{∘}).$$</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>$$\frac{\sqrt{2}}{2}$$</t>
+          <t>$$\frac{\sqrt{6}-\sqrt{2}}{4}$$</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1329,16 +1261,8 @@
           <t>numeric</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>s3</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>h3</t>
-        </is>
-      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
@@ -1351,44 +1275,40 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>trig2</t>
+          <t>trig3</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>hint</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Value of sin(45°)</t>
+          <t>Recall the sine difference formula</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>What is $$sin(45^{∘})$$?</t>
+          <t>What is the formula for $sin(A-B)$?</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>$$\frac{\sqrt{2}}{2}$$</t>
+          <t>$$sin(A)cos(B) - cos(A)sin(B)$$</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>numeric</t>
+          <t>algebra</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>s4</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>h3</t>
-        </is>
-      </c>
+          <t>h1</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
@@ -1401,7 +1321,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>trig2</t>
+          <t>trig3</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1411,32 +1331,32 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Value of cos(30°)</t>
+          <t>Identify A and B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>What is $$cos(30^{∘})$$?</t>
+          <t>In $sin(45^{∘}−30^{∘})$, what are A and B?</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>$$\frac{\sqrt{3}}{2}$$</t>
+          <t>$$A=45^\circ, B=30^\circ$$</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>numeric</t>
+          <t>algebra</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>s5</t>
+          <t>s1</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>h3</t>
+          <t>h1</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -1451,44 +1371,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>trig2</t>
+          <t>trig3</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>hint</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Value of sin(30°)</t>
+          <t>Evaluate trigonometric values</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>What is $$sin(30^{∘})$$?</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>$$\frac{1}{2}$$</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
+          <t>Determine the sine and cosine values for $A=45^\circ$ and $B=30^\circ$.</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>s6</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>h3</t>
-        </is>
-      </c>
+          <t>h2</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
@@ -1501,34 +1409,42 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>trig2</t>
+          <t>trig3</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>hint</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Substitute and simplify</t>
+          <t>Find $sin(45^\circ)$</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Substitute the values into the formula and simplify the expression.</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
+          <t>What is the exact value of $sin(45^\circ)$?</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>$$\frac{\sqrt{2}}{2}$$</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>h4</t>
+          <t>s2</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>h3</t>
+          <t>h2</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -1543,24 +1459,20 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>trig2</t>
+          <t>trig3</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>step</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Combine terms</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Combine the terms to get the final exact value.</t>
-        </is>
-      </c>
+          <t>Evaluate the expression $$sin(135^{∘}−120^{∘}).$$</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>$$\frac{\sqrt{6}-\sqrt{2}}{4}$$</t>
@@ -1571,16 +1483,8 @@
           <t>numeric</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>s7</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>h4</t>
-        </is>
-      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
@@ -1598,31 +1502,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>problem</t>
+          <t>hint</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Using Sum and Difference Identities to Evaluate the Difference of Angles</t>
+          <t>Recall the sine difference formula</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Use the sum and difference identities to evaluate the difference of the angles and show that part a equals part b.</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
+          <t>What is the formula for $sin(A-B)$?</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>$$sin(A)cos(B) - cos(A)sin(B)$$</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>algebra</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>https://openstax.org/books/precalculus-2e/pages/7-2-sum-and-difference-identities</t>
-        </is>
-      </c>
+      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
@@ -1636,27 +1548,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>step</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>evaluate the expression $$sin(45^{∘}−30^{∘})$$</t>
+          <t>Identify A and B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>$$\frac{\sqrt{6}-\sqrt{2}}{4}$$</t>
+          <t>In $sin(135^{∘}−120^{∘})$, what are A and B?</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>numeric</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+          <t>$$A=135^\circ, B=120^\circ$$</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>algebra</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>s1</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
@@ -1679,19 +1603,19 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Apply the sine difference formula</t>
+          <t>Evaluate trigonometric values</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Recall that $$sin(A−B) = sin(A)cos(B) - cos(A)sin(B)$$.</t>
+          <t>Determine the sine and cosine values for $A=135^\circ$ and $B=120^\circ$.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>h1</t>
+          <t>h2</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
@@ -1717,32 +1641,32 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Identify A and B</t>
+          <t>Find $cos(120^\circ)$</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>In $$sin(45^{∘}−30^{∘})$$, what are A and B?</t>
+          <t>What is the exact value of $cos(120^\circ)$?</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>$$A = 45^{∘}, B = 30^{∘}$$</t>
+          <t>$$-\frac{1}{2}$$</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>algebraic</t>
+          <t>numeric</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>s1</t>
+          <t>s2</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>h1</t>
+          <t>h2</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -1757,40 +1681,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>trig3</t>
+          <t>trig4</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>hint</t>
+          <t>problem</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Evaluate trigonometric values</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Find the values of $$sin(45^{∘})$$, $$cos(30^{∘})$$, $$cos(45^{∘})$$, and $$sin(30^{∘})$$.</t>
-        </is>
-      </c>
+          <t>Finding the Exact Value of an Expression Involving an Inverse Trigonometric Function</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>h1</t>
-        </is>
-      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>https://openstax.org/books/precalculus-2e/pages/7-2-sum-and-difference-identities</t>
+        </is>
+      </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
@@ -1799,44 +1715,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>trig3</t>
+          <t>trig4</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>step</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Value of sin(45°)</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>What is $$sin(45^{∘})$$?</t>
-        </is>
-      </c>
+          <t>Find the exact value of $$sin(cos^{−1}\frac{1}{2}+sin^{−1}\frac{3}{5}).$$</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>$$\frac{\sqrt{2}}{2}$$</t>
+          <t>$$\frac{4\sqrt{3}+3}{10}$$</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>numeric</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>s2</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
+          <t>algebraic</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
@@ -1849,44 +1753,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>trig3</t>
+          <t>trig4</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>hint</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Value of cos(30°)</t>
+          <t>Apply the sum identity for sine</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>What is $$cos(30^{∘})$$?</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>$$\frac{\sqrt{3}}{2}$$</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
+          <t>Recall the sum identity for sine: $$sin(A+B) = sinAcosB + cosAsinB$$</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>s3</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
+          <t>h1</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
@@ -1899,7 +1791,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>trig3</t>
+          <t>trig4</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1909,35 +1801,39 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Value of cos(45°)</t>
+          <t>Identify A and B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>What is $$cos(45^{∘})$$?</t>
+          <t>What are A and B in the expression $$sin(cos^{−1}\frac{1}{2}+sin^{−1}\frac{3}{5})$$?</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>$$\frac{\sqrt{2}}{2}$$</t>
+          <t>$$A=cos^{−1}\frac{1}{2}, B=sin^{−1}\frac{3}{5}$$</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>numeric</t>
+          <t>mc</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>s4</t>
+          <t>s1</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>h2</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>h1</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>$$A=cos^{−1}\frac{1}{2}, B=sin^{−1}\frac{3}{5}$$|$$A=sin^{−1}\frac{1}{2}, B=cos^{−1}\frac{3}{5}$$|$$A=\frac{1}{2}, B=\frac{3}{5}$$|$$A=cos^{−1}\frac{3}{5}, B=sin^{−1}\frac{1}{2}$$</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
@@ -1949,42 +1845,34 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>trig3</t>
+          <t>trig4</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>hint</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Value of sin(30°)</t>
+          <t>Determine all necessary trigonometric values</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>What is $$sin(30^{∘})$$?</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>$$\frac{1}{2}$$</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
+          <t>For $$A = cos^{−1}\frac{1}{2}$$ and $$B = sin^{−1}\frac{3}{5}$$, find $$sinA, cosA, sinB, cosB$$.</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>s5</t>
+          <t>h2</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>h2</t>
+          <t>h1</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -1999,29 +1887,37 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>trig3</t>
+          <t>trig4</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>hint</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Substitute and simplify</t>
+          <t>Find sinA and cosA</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Substitute the values into the formula and simplify the expression.</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+          <t>If $$A = cos^{−1}\frac{1}{2}$$, what are $$sinA$$ and $$cosA$$?</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>$$sinA=\frac{\sqrt{3}}{2}, cosA=\frac{1}{2}$$</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>mc</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>h3</t>
+          <t>s2</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2029,7 +1925,11 @@
           <t>h2</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>$$sinA=\frac{\sqrt{3}}{2}, cosA=\frac{1}{2}$$|$$sinA=\frac{1}{2}, cosA=\frac{\sqrt{3}}{2}$$|$$sinA=\frac{\sqrt{3}}{2}, cosA=\frac{\sqrt{3}}{2}$$|$$sinA=\frac{1}{2}, cosA=\frac{1}{2}$$</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
@@ -2041,7 +1941,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>trig3</t>
+          <t>trig4</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2051,35 +1951,39 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Combine terms</t>
+          <t>Find sinB and cosB</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Combine the terms to get the final exact value.</t>
+          <t>If $$B = sin^{−1}\frac{3}{5}$$, what are $$sinB$$ and $$cosB$$?</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>$$\frac{\sqrt{6}-\sqrt{2}}{4}$$</t>
+          <t>$$sinB=\frac{3}{5}, cosB=\frac{4}{5}$$</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>numeric</t>
+          <t>mc</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>s6</t>
+          <t>s3</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>h3</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>h2</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>$$sinB=\frac{3}{5}, cosB=\frac{4}{5}$$|$$sinB=\frac{4}{5}, cosB=\frac{3}{5}$$|$$sinB=\frac{3}{5}, cosB=\frac{3}{5}$$|$$sinB=\frac{4}{5}, cosB=\frac{4}{5}$$</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
@@ -2089,31 +1993,11 @@
       <c r="P36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>trig3</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>step</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>evaluate the expression $$sin(135^{∘}−120^{∘})$$</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>$$\frac{\sqrt{6}-\sqrt{2}}{4}$$</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
@@ -2129,36 +2013,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>trig3</t>
+          <t>trig5</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>hint</t>
+          <t>problem</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Apply the sine difference formula</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Recall that $$sin(A−B) = sin(A)cos(B) - cos(A)sin(B)$$.</t>
-        </is>
-      </c>
+          <t>Finding the Exact Value of an Expression Involving Tangent</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>h1</t>
-        </is>
-      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>https://openstax.org/books/precalculus-2e/pages/7-2-sum-and-difference-identities</t>
+        </is>
+      </c>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
@@ -2167,27 +2047,23 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>trig3</t>
+          <t>trig5</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>step</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Identify A and B</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>In $$sin(135^{∘}−120^{∘})$$, what are A and B?</t>
-        </is>
-      </c>
+          <t>Find the exact value of $$tan(\frac{π}{6}+\frac{π}{4}).$$</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>$$A = 135^{∘}, B = 120^{∘}$$</t>
+          <t>$$2+\sqrt{3}$$</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2195,16 +2071,8 @@
           <t>algebraic</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>s1</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>h1</t>
-        </is>
-      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
@@ -2217,7 +2085,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>trig3</t>
+          <t>trig5</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2227,26 +2095,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Evaluate trigonometric values</t>
+          <t>Apply the sum identity for tangent</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Find the values of $$sin(135^{∘})$$, $$cos(120^{∘})$$, $$cos(135^{∘})$$, and $$sin(120^{∘})$$.</t>
+          <t>Recall the sum identity for tangent: $$tan(A+B) = \frac{tanA + tanB}{1 - tanAtanB}$$</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>h2</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
           <t>h1</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
@@ -2259,7 +2123,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>trig3</t>
+          <t>trig5</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2269,35 +2133,39 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Value of sin(135°)</t>
+          <t>Identify A and B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>What is $$sin(135^{∘})$$?</t>
+          <t>What are A and B in the expression $$tan(\frac{π}{6}+\frac{π}{4})$$?</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>$$\frac{\sqrt{2}}{2}$$</t>
+          <t>$$A=\frac{π}{6}, B=\frac{π}{4}$$</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>numeric</t>
+          <t>mc</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>s2</t>
+          <t>s1</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>h2</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>h1</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>$$A=\frac{π}{6}, B=\frac{π}{4}$$|$$A=\frac{π}{4}, B=\frac{π}{6}$$|$$A=\frac{π}{6}, B=\frac{π}{6}$$|$$A=\frac{π}{4}, B=\frac{π}{4}$$</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
@@ -2309,42 +2177,34 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>trig3</t>
+          <t>trig5</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>hint</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Value of cos(120°)</t>
+          <t>Evaluate tangent values</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>What is $$cos(120^{∘})$$?</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>$$-\frac{1}{2}$$</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
+          <t>Determine the values of $$tan(\frac{π}{6})$$ and $$tan(\frac{π}{4})$$.</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>s3</t>
+          <t>h2</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>h2</t>
+          <t>h1</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -2359,7 +2219,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>trig3</t>
+          <t>trig5</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2369,17 +2229,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Value of cos(135°)</t>
+          <t>Find tan(pi/6)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>What is $$cos(135^{∘})$$?</t>
+          <t>What is the exact value of $$tan(\frac{π}{6})$$?</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>$$-\frac{\sqrt{2}}{2}$$</t>
+          <t>$$\frac{\sqrt{3}}{3}$$</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2389,7 +2249,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>s4</t>
+          <t>s2</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2409,7 +2269,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>trig3</t>
+          <t>trig5</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2419,17 +2279,17 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Value of sin(120°)</t>
+          <t>Find tan(pi/4)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>What is $$sin(120^{∘})$$?</t>
+          <t>What is the exact value of $$tan(\frac{π}{4})$$?</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>$$\frac{\sqrt{3}}{2}$$</t>
+          <t>$$1$$</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2439,7 +2299,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>s5</t>
+          <t>s3</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2457,38 +2317,14 @@
       <c r="P44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>trig3</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>hint</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Substitute and simplify</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Substitute the values into the formula and simplify the expression.</t>
-        </is>
-      </c>
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>h3</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
@@ -2501,48 +2337,36 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>trig3</t>
+          <t>trig6</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>problem</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Combine terms</t>
+          <t>Finding Multiple Sums and Differences of Angles</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Combine the terms to get the final exact value.</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>$$\frac{\sqrt{6}-\sqrt{2}}{4}$$</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>s6</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>h3</t>
-        </is>
-      </c>
+          <t>Given $$sinα=\frac{3}{5},0&lt;α&lt;\frac{π}{2},cosβ=−\frac{5}{13},π&lt;β&lt;\frac{3π}{2},$$ find</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>https://openstax.org/books/precalculus-2e/pages/7-2-sum-and-difference-identities</t>
+        </is>
+      </c>
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
@@ -2551,32 +2375,36 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>trig4</t>
+          <t>trig6</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>problem</t>
+          <t>step</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Finding the Exact Value of an Expression Involving an Inverse Trigonometric Function</t>
+          <t>$$sin(α+β)$$</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>$$-\frac{63}{65}$$</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>https://openstax.org/books/precalculus-2e/pages/7-2-sum-and-difference-identities</t>
-        </is>
-      </c>
+      <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
@@ -2585,31 +2413,31 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>trig4</t>
+          <t>trig6</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>step</t>
+          <t>hint</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Find the exact value of $$sin(cos^{−1}\frac{1}{2}+sin^{−1}\frac{3}{5}).$$</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">$$\frac{4\sqrt{3}+3}{10}$$ </t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>algebra</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr"/>
+          <t>Determine all necessary trigonometric values</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Before applying the sum identity, find $$cosα, tanα, sinβ, tanβ$$ using the given information and quadrant restrictions.</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
@@ -2623,33 +2451,49 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>trig4</t>
+          <t>trig6</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>hint</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Apply the sine sum identity</t>
+          <t>Find cosα and tanα</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Recall the sum identity for sine: $$sin(A+B) = sinAcosB + cosAsinB$$</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
+          <t>Given $$sinα=\frac{3}{5},0&lt;α&lt;\frac{π}{2}$$, what are $$cosα$$ and $$tanα$$?</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>$$cosα=\frac{4}{5}, tanα=\frac{3}{4}$$</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>mc</t>
+        </is>
+      </c>
       <c r="G49" t="inlineStr">
         <is>
+          <t>s1</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
           <t>h1</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>$$cosα=\frac{4}{5}, tanα=\frac{3}{4}$$|$$cosα=−\frac{4}{5}, tanα=−\frac{3}{4}$$|$$cosα=\frac{4}{5}, tanα=\frac{4}{3}$$|$$cosα=−\frac{4}{5}, tanα=−\frac{4}{3}$$</t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
@@ -2661,7 +2505,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>trig4</t>
+          <t>trig6</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2671,27 +2515,27 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Identify the identity</t>
+          <t>Find sinβ and tanβ</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Which trigonometric identity is appropriate for $$sin(A+B)$$?</t>
+          <t>Given $$cosβ=−\frac{5}{13},π&lt;β&lt;\frac{3π}{2}$$, what are $$sinβ$$ and $$tanβ$$?</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>$$sinAcosB + cosAsinB$$</t>
+          <t>$$sinβ=−\frac{12}{13}, tanβ=\frac{12}{5}$$</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>algebra</t>
+          <t>mc</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>s1</t>
+          <t>s2</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2699,7 +2543,11 @@
           <t>h1</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>$$sinβ=−\frac{12}{13}, tanβ=\frac{12}{5}$$|$$sinβ=\frac{12}{13}, tanβ=−\frac{12}{5}$$|$$sinβ=−\frac{12}{13}, tanβ=−\frac{12}{5}$$|$$sinβ=\frac{12}{13}, tanβ=\frac{12}{5}$$</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
@@ -2711,7 +2559,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>trig4</t>
+          <t>trig6</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2721,12 +2569,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Determine individual trigonometric values</t>
+          <t>Apply the sum identity for sine</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Find the values of $$sin(cos^{−1}\frac{1}{2})$$, $$cos(cos^{−1}\frac{1}{2})$$, $$sin(sin^{−1}\frac{3}{5})$$, and $$cos(sin^{−1}\frac{3}{5})$$.</t>
+          <t>Recall the sum identity for sine: $$sin(A+B) = sinAcosB + cosAsinB$$</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -2753,7 +2601,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>trig4</t>
+          <t>trig6</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2763,27 +2611,27 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Evaluate $$cos(cos^{−1}\frac{1}{2})$$</t>
+          <t>Substitute values into identity</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>What is the value of $$cos(cos^{−1}\frac{1}{2})$$?</t>
+          <t>Substitute the known values of $$sinα, cosα, sinβ, cosβ$$ into the identity.</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">$$\frac{1}{2}$$ </t>
+          <t>$$(\frac{3}{5})(-\frac{5}{13}) + (\frac{4}{5})(-\frac{12}{13})$$</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>algebra</t>
+          <t>algebraic</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>s2</t>
+          <t>s3</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2803,44 +2651,32 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>trig4</t>
+          <t>trig6</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>step</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Evaluate $$sin(cos^{−1}\frac{1}{2})$$</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>If $$A = cos^{−1}\frac{1}{2}$$, what is $$sinA$$? (Hint: Draw a right triangle or use $$sin^2A + cos^2A = 1$$)</t>
-        </is>
-      </c>
+          <t>$$cos(α+β)$$</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">$$\frac{\sqrt{3}}{2}$$ </t>
+          <t>$$\frac{16}{65}$$</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>algebra</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>s3</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
@@ -2853,44 +2689,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>trig4</t>
+          <t>trig6</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>hint</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Evaluate $$sin(sin^{−1}\frac{3}{5})$$</t>
+          <t>Apply the sum identity for cosine</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>What is the value of $$sin(sin^{−1}\frac{3}{5})$$?</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">$$\frac{3}{5}$$ </t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>algebra</t>
-        </is>
-      </c>
+          <t>Recall the sum identity for cosine: $$cos(A+B) = cosAcosB - sinAsinB$$</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>s4</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
+          <t>h1</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
@@ -2903,7 +2727,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>trig4</t>
+          <t>trig6</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2913,32 +2737,32 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Evaluate $$cos(sin^{−1}\frac{3}{5})$$</t>
+          <t>Substitute values into identity</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>If $$B = sin^{−1}\frac{3}{5}$$, what is $$cosB$$? (Hint: Draw a right triangle or use $$sin^2B + cos^2B = 1$$)</t>
+          <t>Substitute the known values of $$sinα, cosα, sinβ, cosβ$$ into the identity.</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">$$\frac{4}{5}$$ </t>
+          <t>$$(\frac{4}{5})(-\frac{5}{13}) - (\frac{3}{5})(-\frac{12}{13})$$</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>algebra</t>
+          <t>algebraic</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>s5</t>
+          <t>s1</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>h2</t>
+          <t>h1</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -2951,12 +2775,32 @@
       <c r="P55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr"/>
-      <c r="B56" t="inlineStr"/>
-      <c r="C56" t="inlineStr"/>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>trig6</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>step</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>$$tan(α+β)$$</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>$$-\frac{63}{16}$$</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
@@ -2971,32 +2815,36 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>trig5</t>
+          <t>trig6</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>problem</t>
+          <t>hint</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Finding the Exact Value of an Expression Involving Tangent</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
+          <t>Apply the sum identity for tangent</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Recall the sum identity for tangent: $$tan(A+B) = \frac{tanA + tanB}{1 - tanAtanB}$$</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>https://openstax.org/books/precalculus-2e/pages/7-2-sum-and-difference-identities</t>
-        </is>
-      </c>
+      <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
@@ -3005,32 +2853,44 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>trig5</t>
+          <t>trig6</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>step</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Find the exact value of $$tan(\frac{π}{6}+\frac{π}{4}).$$</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
+          <t>Substitute values into identity</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Substitute the known values of $$tanα$$ and $$tanβ$$ into the identity.</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">$$2+\sqrt{3}$$ </t>
+          <t>$$\frac{\frac{3}{4} + \frac{12}{5}}{1 - (\frac{3}{4})(\frac{12}{5})}$$</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>algebra</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
+          <t>algebraic</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>s1</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
@@ -3043,31 +2903,31 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>trig5</t>
+          <t>trig6</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>hint</t>
+          <t>step</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Apply the tangent sum identity</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Recall the sum identity for tangent: $$tan(A+B) = \frac{tanA + tanB}{1 - tanAtanB}$$</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>h1</t>
-        </is>
-      </c>
+          <t>$$tan(α−β)$$</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>$$-\frac{33}{56}$$</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
@@ -3081,44 +2941,32 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>trig5</t>
+          <t>trig6</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>hint</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Identify the identity</t>
+          <t>Apply the difference identity for tangent</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Which trigonometric identity is appropriate for $$tan(A+B)$$?</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">$$\frac{tanA + tanB}{1 - tanAtanB}$$ </t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>algebra</t>
-        </is>
-      </c>
+          <t>Recall the difference identity for tangent: $$tan(A-B) = \frac{tanA - tanB}{1 + tanAtanB}$$</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>s1</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
           <t>h1</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
@@ -3131,29 +2979,37 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>trig5</t>
+          <t>trig6</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>hint</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Recall special angle values</t>
+          <t>Substitute values into identity</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Determine the values of $$tan(\frac{π}{6})$$ and $$tan(\frac{π}{4})$$.</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
+          <t>Substitute the known values of $$tanα$$ and $$tanβ$$ into the identity.</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>$$\frac{\frac{3}{4} - \frac{12}{5}}{1 + (\frac{3}{4})(\frac{12}{5})}$$</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>algebraic</t>
+        </is>
+      </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>h2</t>
+          <t>s1</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3173,48 +3029,32 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>trig5</t>
+          <t>trig7</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>problem</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Evaluate $$tan(\frac{π}{6})$$</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>What is the exact value of $$tan(\frac{π}{6})$$?</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">$$\frac{\sqrt{3}}{3}$$ </t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>algebra</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>s2</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
+          <t>Finding a Cofunction with the Same Value as the Given Expression</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>https://openstax.org/books/precalculus-2e/pages/7-2-sum-and-difference-identities</t>
+        </is>
+      </c>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
@@ -3223,27 +3063,23 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>trig5</t>
+          <t>trig7</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>step</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Evaluate $$tan(\frac{π}{4})$$</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>What is the exact value of $$tan(\frac{π}{4})$$?</t>
-        </is>
-      </c>
+          <t>Write $$\tan\left(\frac{\pi}{9}\right)$$ in terms of its cofunction.</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>$$1$$</t>
+          <t>$$\cot\left(\frac{7\pi}{18}\right)$$</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3251,16 +3087,8 @@
           <t>algebra</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>s3</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
@@ -3271,13 +3099,33 @@
       <c r="P63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr"/>
-      <c r="B64" t="inlineStr"/>
-      <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr"/>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>trig7</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>hint</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Recall cofunction identities</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Remember that trigonometric cofunction identities relate the value of a trigonometric function of an angle to the value of its cofunction at the complementary angle. For tangent, $$\tan(\theta) = \cot\left(\frac{\pi}{2} - \theta\right)$$.</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
@@ -3291,23 +3139,27 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>trig6</t>
+          <t>trig7</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>step</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>$$sin(α+β)$$</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
+          <t>Identify the angle</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>What is the angle $$\theta$$ in the given expression $$\tan\left(\frac{\pi}{9}\right)$$?</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">$$-\frac{63}{65}$$ </t>
+          <t>$$\frac{\pi}{9}$$</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3315,8 +3167,16 @@
           <t>algebra</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>s1</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
@@ -3329,7 +3189,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>trig6</t>
+          <t>trig7</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3339,22 +3199,26 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Recall the sine sum identity</t>
+          <t>Apply the identity</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>The identity for $$sin(α+β)$$ is $$sinαcosβ + cosαsinβ$$.</t>
+          <t>Substitute the angle into the cofunction identity for tangent.</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
+          <t>h2</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
           <t>h1</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
@@ -3367,7 +3231,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>trig6</t>
+          <t>trig7</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3377,17 +3241,17 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Identify the identity</t>
+          <t>Calculate the complementary angle</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>What is the formula for $$sin(α+β)$$?</t>
+          <t>What is $$\frac{\pi}{2} - \frac{\pi}{9}$$?</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>$$sinαcosβ + cosαsinβ$$</t>
+          <t>$$\frac{7\pi}{18}$$</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3397,12 +3261,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>s1</t>
+          <t>s2</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>h1</t>
+          <t>h2</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -3415,38 +3279,14 @@
       <c r="P67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>trig6</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>hint</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Determine missing trigonometric values</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Find $$cosα$$ and $$sinβ$$ using the given information and quadrant restrictions.</t>
-        </is>
-      </c>
+      <c r="A68" t="inlineStr"/>
+      <c r="B68" t="inlineStr"/>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>h1</t>
-        </is>
-      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
@@ -3459,48 +3299,32 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>trig6</t>
+          <t>trig8</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>problem</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Find $$cosα$$</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Given $$sinα=\frac{3}{5}$$ and $$0&lt;α&lt;\frac{π}{2}$$, what is $$cosα$$?</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">$$\frac{4}{5}$$ </t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>algebra</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>s2</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
+          <t>Verifying an Identity Involving Sine</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>https://openstax.org/books/precalculus-2e/pages/7-2-sum-and-difference-identities</t>
+        </is>
+      </c>
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
@@ -3509,27 +3333,23 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>trig6</t>
+          <t>trig8</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>step</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Find $$sinβ$$</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Given $$cosβ=−\frac{5}{13}$$ and $$π&lt;β&lt;\frac{3π}{2}$$, what is $$sinβ$$?</t>
-        </is>
-      </c>
+          <t>Evaluate the expression $$\sin(\alpha+\beta)+\sin(\alpha-\beta)$$</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">$$-\frac{12}{13}$$ </t>
+          <t>$$2\sin\alpha\cos\beta$$</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3537,16 +3357,8 @@
           <t>algebra</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>s3</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
@@ -3559,31 +3371,31 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>trig6</t>
+          <t>trig8</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>step</t>
+          <t>hint</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>$$cos(α+β)$$</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">$$\frac{16}{65}$$ </t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>algebra</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr"/>
+          <t>Recall sum and difference identities for sine</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Remember the sum and difference identities for sine: $$\sin(A+B) = \sin A \cos B + \cos A \sin B$$ and $$\sin(A-B) = \sin A \cos B - \cos A \sin B$$.</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
@@ -3597,32 +3409,44 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>trig6</t>
+          <t>trig8</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>hint</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Recall the cosine sum identity</t>
+          <t>Expand $$\sin(\alpha+\beta)$$</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>The identity for $$cos(α+β)$$ is $$cosαcosβ - sinαsinβ$$.</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
+          <t>What is the expansion of $$\sin(\alpha+\beta)$$?</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>$$\sin\alpha\cos\beta + \cos\alpha\sin\beta$$</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>algebra</t>
+        </is>
+      </c>
       <c r="G72" t="inlineStr">
         <is>
+          <t>s1</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
           <t>h1</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
@@ -3635,7 +3459,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>trig6</t>
+          <t>trig8</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3645,17 +3469,17 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Identify the identity</t>
+          <t>Expand $$\sin(\alpha-\beta)$$</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>What is the formula for $$cos(α+β)$$?</t>
+          <t>What is the expansion of $$\sin(\alpha-\beta)$$?</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>$$cosαcosβ - sinαsinβ$$</t>
+          <t>$$\sin\alpha\cos\beta - \cos\alpha\sin\beta$$</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3665,7 +3489,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>s1</t>
+          <t>s2</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3685,7 +3509,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>trig6</t>
+          <t>trig8</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3695,12 +3519,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Use previously found values</t>
+          <t>Combine the expanded terms</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Use the values of $$sinα, cosα, sinβ, cosβ$$ determined earlier.</t>
+          <t>Add the expanded forms of $$\sin(\alpha+\beta)$$ and $$\sin(\alpha-\beta)$$ together.</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
@@ -3727,7 +3551,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>trig6</t>
+          <t>trig8</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3737,17 +3561,17 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>What is $$sinα$$?</t>
+          <t>Simplify the sum</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>What is the value of $$sinα$$?</t>
+          <t>What do you get when you add $$(\sin\alpha\cos\beta + \cos\alpha\sin\beta) + (\sin\alpha\cos\beta - \cos\alpha\sin\beta)$$?</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">$$\frac{3}{5}$$ </t>
+          <t>$$2\sin\alpha\cos\beta$$</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3757,7 +3581,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>s2</t>
+          <t>s3</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3775,46 +3599,14 @@
       <c r="P75" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>trig6</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>scaffold</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>What is $$cosα$$?</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>What is the value of $$cosα$$?</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">$$\frac{4}{5}$$ </t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>algebra</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>s3</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
+      <c r="A76" t="inlineStr"/>
+      <c r="B76" t="inlineStr"/>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
@@ -3827,48 +3619,32 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>trig6</t>
+          <t>trig9</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>problem</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>What is $$sinβ$$?</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>What is the value of $$sinβ$$?</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">$$-\frac{12}{13}$$ </t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>algebra</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>s4</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
+          <t>Verifying an Identity Involving Tangent</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>https://openstax.org/books/precalculus-2e/pages/7-2-sum-and-difference-identities</t>
+        </is>
+      </c>
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
@@ -3877,27 +3653,23 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>trig6</t>
+          <t>trig9</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>step</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>What is $$cosβ$$?</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>What is the value of $$cosβ$$?</t>
-        </is>
-      </c>
+          <t>Evaluate the expression $$\frac{\sin(\alpha-\beta)}{\cos\alpha\cos\beta}$$</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">$$-\frac{5}{13}$$ </t>
+          <t>$$\tan\alpha - \tan\beta$$</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3905,16 +3677,8 @@
           <t>algebra</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>s5</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
@@ -3927,31 +3691,31 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>trig6</t>
+          <t>trig9</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>step</t>
+          <t>hint</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>$$tan(α+β)$$</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">$$-\frac{63}{16}$$ </t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>algebra</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr"/>
+          <t>Recall difference identity for sine</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Remember the difference identity for sine: $$\sin(A-B) = \sin A \cos B - \cos A \sin B$$.</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
@@ -3965,32 +3729,44 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>trig6</t>
+          <t>trig9</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>hint</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Recall the tangent sum identity</t>
+          <t>Expand the numerator</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>The identity for $$tan(α+β)$$ is $$\frac{tanα + tanβ}{1 - tanαtanβ}$$. Alternatively, you can use $$\frac{sin(α+β)}{cos(α+β)}$$.</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
+          <t>What is the expansion of $$\sin(\alpha-\beta)$$?</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>$$\sin\alpha\cos\beta - \cos\alpha\sin\beta$$</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>algebra</t>
+        </is>
+      </c>
       <c r="G80" t="inlineStr">
         <is>
+          <t>s1</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
           <t>h1</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
@@ -4003,37 +3779,29 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>trig6</t>
+          <t>trig9</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>hint</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Identify the identity</t>
+          <t>Separate the fraction</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>What is the formula for $$tan(α+β)$$?</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">$$\frac{tanα + tanβ}{1 - tanαtanβ}$$ </t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>algebra</t>
-        </is>
-      </c>
+          <t>Once the numerator is expanded, divide each term in the numerator by the denominator $$\cos\alpha\cos\beta$$.</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>s1</t>
+          <t>h2</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4053,34 +3821,42 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>trig6</t>
+          <t>trig9</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>hint</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Determine $$tanα$$ and $$tanβ$$</t>
+          <t>Split the fraction</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Find $$tanα$$ and $$tanβ$$ using the given information and quadrant restrictions.</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
+          <t>Rewrite $$\frac{\sin\alpha\cos\beta - \cos\alpha\sin\beta}{\cos\alpha\cos\beta}$$ as two separate fractions.</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>$$\frac{\sin\alpha\cos\beta}{\cos\alpha\cos\beta} - \frac{\cos\alpha\sin\beta}{\cos\alpha\cos\beta}$$</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>algebra</t>
+        </is>
+      </c>
       <c r="G82" t="inlineStr">
         <is>
+          <t>s2</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
           <t>h2</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>h1</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -4095,37 +3871,29 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>trig6</t>
+          <t>trig9</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>hint</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Find $$tanα$$</t>
+          <t>Simplify using basic identities</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Given $$sinα=\frac{3}{5}$$ and $$cosα=\frac{4}{5}$$, what is $$tanα$$?</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">$$\frac{3}{4}$$ </t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>algebra</t>
-        </is>
-      </c>
+          <t>Use the identity $$\tan x = \frac{\sin x}{\cos x}$$ to simplify each term.</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>s2</t>
+          <t>h3</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4145,7 +3913,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>trig6</t>
+          <t>trig9</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4155,17 +3923,17 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Find $$tanβ$$</t>
+          <t>Simplify each term</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Given $$sinβ=-\frac{12}{13}$$ and $$cosβ=-\frac{5}{13}$$, what is $$tanβ$$?</t>
+          <t>Simplify $$\frac{\sin\alpha\cos\beta}{\cos\alpha\cos\beta}$$ and $$\frac{\cos\alpha\sin\beta}{\cos\alpha\cos\beta}$$.</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">$$\frac{12}{5}$$ </t>
+          <t>$$\tan\alpha - \tan\beta$$</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -4180,7 +3948,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>h2</t>
+          <t>h3</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -4195,36 +3963,32 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>trig6</t>
+          <t>trig10</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>step</t>
+          <t>problem</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>$$tan(α−β)$$</t>
+          <t>Using Sum and Difference Formulas to Solve an Application Problem</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">$$-\frac{33}{56}$$ </t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>algebra</t>
-        </is>
-      </c>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>https://openstax.org/books/precalculus-2e/pages/7-2-sum-and-difference-identities</t>
+        </is>
+      </c>
       <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
@@ -4233,31 +3997,31 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>trig6</t>
+          <t>trig10</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>hint</t>
+          <t>step</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Recall the tangent difference identity</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>The identity for $$tan(α−β)$$ is $$\frac{tanα - tanβ}{1 + tanαtanβ}$$.</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>h1</t>
-        </is>
-      </c>
+          <t>Derive the formula for the acute angle $$θ$$ between two lines $$L_{1}$$ and $$L_{2}$$ with slopes $$m_{1}$$ and $$m_{2}$$ respectively.</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>$$tanθ=\frac{m_{2}−m_{1}}{1+m_{1}m_{2}}$$</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>algebra</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
@@ -4271,44 +4035,32 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>trig6</t>
+          <t>trig10</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>hint</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Identify the identity</t>
+          <t>Relating angles</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>What is the formula for $$tan(α−β)$$?</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">$$\frac{tanα - tanβ}{1 + tanαtanβ}$$ </t>
-        </is>
-      </c>
+          <t>Recall that the angle $$θ$$ between two lines can be expressed in terms of the angles $$θ_{1}$$ and $$θ_{2}$$ that each line makes with the positive x-axis. Specifically, $$θ = θ_{2} - θ_{1}$$.</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
-          <t>algebra</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>s1</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
           <t>h1</t>
         </is>
       </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
@@ -4321,29 +4073,37 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>trig6</t>
+          <t>trig10</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>hint</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Use previously found tangent values</t>
+          <t>Express $$tanθ$$</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Use the values of $$tanα$$ and $$tanβ$$ determined earlier.</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
+          <t>How can you express $$tanθ$$ in terms of $$tanθ_{1}$$ and $$tanθ_{2}$$?</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>$$tanθ = tan(θ_{2} - θ_{1})$$</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>algebra</t>
+        </is>
+      </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>h2</t>
+          <t>s1</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4363,44 +4123,36 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>trig6</t>
+          <t>trig10</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>hint</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>What is $$tanα$$?</t>
+          <t>Tangent difference identity</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>What is the value of $$tanα$$?</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">$$\frac{3}{4}$$ </t>
-        </is>
-      </c>
+          <t>Use the tangent difference formula: $$tan(A - B) = \frac{tan A - tan B}{1 + tan A tan B}$$.</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>algebra</t>
+          <t>h2</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>s2</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
+          <t>h1</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
@@ -4413,7 +4165,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>trig6</t>
+          <t>trig10</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4423,17 +4175,17 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>What is $$tanβ$$?</t>
+          <t>Apply formula</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>What is the value of $$tanβ$$?</t>
+          <t>Apply the tangent difference formula to $$tan(θ_{2} - θ_{1})$$.</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">$$\frac{12}{5}$$ </t>
+          <t>$$\frac{tanθ_{2}−tanθ_{1}}{1+tanθ_{1}tanθ_{2}}$$</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4443,7 +4195,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>s3</t>
+          <t>s2</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4463,32 +4215,40 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>trig7</t>
+          <t>trig10</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>problem</t>
+          <t>hint</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Finding a Cofunction with the Same Value as the Given Expression</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr"/>
+          <t>Substitute slopes</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Substitute $$tanθ_{1}=m_{1}$$ and $$tanθ_{2}=m_{2}$$ into the expression.</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>h3</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>https://openstax.org/books/precalculus-2e/pages/7-2-sum-and-difference-identities</t>
-        </is>
-      </c>
+      <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr"/>
@@ -4497,23 +4257,27 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>trig7</t>
+          <t>trig10</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>step</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Write $$tan\frac{π}{9}$$ in terms of its cofunction.</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr"/>
+          <t>Final substitution</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Substitute $$m_{1}$$ and $$m_{2}$$ into the expression.</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>$$cot\frac{7π}{18}$$</t>
+          <t>$$\frac{m_{2}−m_{1}}{1+m_{1}m_{2}}$$</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4521,8 +4285,16 @@
           <t>algebra</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>s3</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>h3</t>
+        </is>
+      </c>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
@@ -4533,33 +4305,13 @@
       <c r="P92" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>trig7</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>hint</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Recall Cofunction Identities</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Remember the cofunction identities relating tangent and cotangent: `tan(θ) = cot(π/2 - θ)`. </t>
-        </is>
-      </c>
+      <c r="A93" t="inlineStr"/>
+      <c r="B93" t="inlineStr"/>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>h1</t>
-        </is>
-      </c>
+      <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
@@ -4573,48 +4325,32 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>trig7</t>
+          <t>trig11</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>problem</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Identify θ</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>In `tan(π/9)`, what is the value of θ?</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>$$\frac{π}{9}$$</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>algebra</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>s1</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>h1</t>
-        </is>
-      </c>
+          <t>Investigating a Guy-wire Problem</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>https://openstax.org/books/precalculus-2e/pages/7-2-sum-and-difference-identities</t>
+        </is>
+      </c>
       <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr"/>
@@ -4623,36 +4359,32 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>trig7</t>
+          <t>trig11</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>hint</t>
+          <t>step</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Apply the Identity</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Substitute θ into the cofunction identity `cot(π/2 - θ)`. </t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>h1</t>
-        </is>
-      </c>
+          <t>Find the angle $$α$$ between the wires.</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>$$4.57^\circ$$</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
@@ -4665,44 +4397,32 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>trig7</t>
+          <t>trig11</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>hint</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Calculate the Angle</t>
+          <t>Define angles</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>What is `π/2 - π/9`?</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>$$\frac{7π}{18}$$</t>
-        </is>
-      </c>
+          <t>Let $$θ_{R}$$ be the angle wire R makes with the ground, and $$θ_{S}$$ be the angle wire S makes with the ground. These form two right triangles with the pole.</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
-          <t>algebra</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>s2</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
+          <t>h1</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
@@ -4715,32 +4435,48 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>trig8</t>
+          <t>trig11</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>problem</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Verifying an Identity Involving Sine</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
+          <t>Tangent of $$θ_{R}$$</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>What is the value of $$tan(θ_{R})$$?</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>$$47/50$$</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>s1</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>https://openstax.org/books/precalculus-2e/pages/7-2-sum-and-difference-identities</t>
-        </is>
-      </c>
+      <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr"/>
@@ -4749,31 +4485,35 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>trig8</t>
+          <t>trig11</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>step</t>
+          <t>hint</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Evaluate the expression $$sin(α+β)+sin(α−β)$$</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>$$2sinαcosβ$$</t>
-        </is>
-      </c>
+          <t>Calculate individual angles</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Use the inverse tangent function to find $$θ_{R}$$ and $$θ_{S}$$ from their tangent ratios. Remember $$tan(\text{angle}) = \text{opposite} / \text{adjacent}$$.</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>algebra</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr"/>
+          <t>h2</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
@@ -4787,32 +4527,44 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>trig8</t>
+          <t>trig11</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>hint</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Recall Sum and Difference Identities for Sine</t>
+          <t>Value of $$θ_{S}$$</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Remember the sum and difference identities for sine: `sin(A+B) = sinAcosB + cosAsinB` and `sin(A-B) = sinAcosB - cosAsinB`.</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr"/>
+          <t>What is the value of $$θ_{S}$$ in degrees, rounded to two decimal places?</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>$$38.66^\circ$$</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>h1</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr"/>
+          <t>s2</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
@@ -4825,44 +4577,36 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>trig8</t>
+          <t>trig11</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>hint</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Expand sin(α+β)</t>
+          <t>Find the angle difference</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Using the sum identity, what is `sin(α+β)`?</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>$$sinαcosβ + cosαsinβ$$</t>
-        </is>
-      </c>
+          <t>The angle $$α$$ between the wires is the difference between the angle of the higher wire ($$θ_{R}$$) and the angle of the lower wire ($$θ_{S}$$).</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>algebra</t>
+          <t>h3</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>s1</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>h1</t>
-        </is>
-      </c>
+          <t>h2</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
@@ -4875,34 +4619,42 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>trig8</t>
+          <t>trig11</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>hint</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Expand sin(α-β)</t>
+          <t>Calculate $$α$$</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Using the difference identity, what is `sin(α-β)`?</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr"/>
+          <t>Using $$θ_{R} \approx 43.23^\circ$$ and $$θ_{S} \approx 38.66^\circ$$, what is $$α$$ in degrees, rounded to two decimal places?</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>$$4.57^\circ$$</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>h2</t>
+          <t>s3</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>h1</t>
+          <t>h3</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -4914,1248 +4666,6 @@
       <c r="O101" t="inlineStr"/>
       <c r="P101" t="inlineStr"/>
     </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>trig8</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>scaffold</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Expand sin(α-β)</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>What is `sin(α-β)`?</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>$$sinαcosβ - cosαsinβ$$</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>algebra</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>s2</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
-      <c r="O102" t="inlineStr"/>
-      <c r="P102" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>trig8</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>hint</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Combine the Expanded Forms</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Add the expanded forms of `sin(α+β)` and `sin(α-β)`. </t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>h3</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>h1,h2</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
-      <c r="O103" t="inlineStr"/>
-      <c r="P103" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>trig8</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>scaffold</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Simplify the Sum</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>What do you get when you add `(sinαcosβ + cosαsinβ)` and `(sinαcosβ - cosαsinβ)`?</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>$$2sinαcosβ$$</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>algebra</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>s3</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>h3</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
-      <c r="O104" t="inlineStr"/>
-      <c r="P104" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>trig9</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>problem</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Verifying an Identity Involving Tangent</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr">
-        <is>
-          <t>https://openstax.org/books/precalculus-2e/pages/7-2-sum-and-difference-identities</t>
-        </is>
-      </c>
-      <c r="M105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
-      <c r="O105" t="inlineStr"/>
-      <c r="P105" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>trig9</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>step</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Evaluate the expression $$\frac{sin(α−β)}{cosαcosβ}$$</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>$$tanα−tanβ$$</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>algebra</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
-      <c r="O106" t="inlineStr"/>
-      <c r="P106" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>trig9</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>hint</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Recall Difference Identity for Sine</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>Remember the difference identity for sine: `sin(A-B) = sinAcosB - cosAsinB`.</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>h1</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
-      <c r="O107" t="inlineStr"/>
-      <c r="P107" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>trig9</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>scaffold</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Expand sin(α-β)</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>Using the difference identity, what is `sin(α-β)`?</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>$$sinαcosβ - cosαsinβ$$</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>algebra</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>s1</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>h1</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
-      <c r="O108" t="inlineStr"/>
-      <c r="P108" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>trig9</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>hint</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Substitute and Separate</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>Substitute the expanded form of `sin(α-β)` into the numerator and then separate the fraction into two terms.</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>h1</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
-      <c r="O109" t="inlineStr"/>
-      <c r="P109" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>trig9</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>scaffold</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Separate the Fraction</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>After substituting, how can you rewrite `$$\frac{sinαcosβ - cosαsinβ}{cosαcosβ}$$` as two separate fractions?</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>$$\frac{sinαcosβ}{cosαcosβ} - \frac{cosαsinβ}{cosαcosβ}$$</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>algebra</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>s2</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
-      <c r="O110" t="inlineStr"/>
-      <c r="P110" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>trig9</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>hint</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Simplify Each Term</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>Simplify each of the two fractions using the definitions of tangent (`tanθ = sinθ/cosθ`).</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr"/>
-      <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>h3</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
-      <c r="O111" t="inlineStr"/>
-      <c r="P111" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>trig9</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>scaffold</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Simplify the First Term</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>What does `$$\frac{sinαcosβ}{cosαcosβ}$$` simplify to?</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>$$tanα$$</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>algebra</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>s3</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>h3</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
-      <c r="O112" t="inlineStr"/>
-      <c r="P112" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>trig9</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>scaffold</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Simplify the Second Term</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>What does `$$\frac{cosαsinβ}{cosαcosβ}$$` simplify to?</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>$$tanβ$$</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>algebra</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>s4</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>h3</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
-      <c r="O113" t="inlineStr"/>
-      <c r="P113" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>trig10</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>problem</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Using Sum and Difference Formulas to Solve an Application Problem</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr"/>
-      <c r="E114" t="inlineStr"/>
-      <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr"/>
-      <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr">
-        <is>
-          <t>https://openstax.org/books/precalculus-2e/pages/7-2-sum-and-difference-identities</t>
-        </is>
-      </c>
-      <c r="M114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
-      <c r="O114" t="inlineStr"/>
-      <c r="P114" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>trig10</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>step</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Derive the formula for the tangent of the acute angle between two lines, $$L_1$$ and $$L_2$$, with slopes $$m_1$$ and $$m_2$$ respectively.</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr"/>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>$$\frac{m_{2}−m_{1}}{1+m_{1}m_{2}}$$</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>algebraic</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr"/>
-      <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
-      <c r="O115" t="inlineStr"/>
-      <c r="P115" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>trig10</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>hint</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Relate slopes to angles</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>Recall that the slope of a line is equal to the tangent of the angle the line makes with the positive x-axis.</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr"/>
-      <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>h1</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
-      <c r="O116" t="inlineStr"/>
-      <c r="P116" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>trig10</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>scaffold</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Identify $$tan\theta_1$$ and $$tan\theta_2$$</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>If $$\theta_1$$ is the angle $$L_1$$ makes with the x-axis and $$\theta_2$$ for $$L_2$$, what are $$tan\theta_1$$ and $$tan\theta_2$$ in terms of $$m_1$$ and $$m_2$$?</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>$$tan\theta_1 = m_1, tan\theta_2 = m_2$$</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>algebraic</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>s1</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>h1</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
-      <c r="O117" t="inlineStr"/>
-      <c r="P117" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>trig10</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>hint</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Angle relationship</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>The angle $$\theta$$ between the lines can be expressed as the difference between the angles $$\theta_1$$ and $$\theta_2$$.</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr"/>
-      <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>h1</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
-      <c r="O118" t="inlineStr"/>
-      <c r="P118" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>trig10</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>scaffold</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Express $$\theta$$</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>How can you express $$\theta$$ using $$\theta_1$$ and $$\theta_2$$?</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>$$\theta = \theta_2 - \theta_1$$</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>algebraic</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>s2</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
-      <c r="O119" t="inlineStr"/>
-      <c r="P119" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>trig10</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>hint</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Tangent difference formula</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>Apply the tangent difference identity: $$tan(A - B) = \frac{tan A - tan B}{1 + tan A tan B}$$.</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>h3</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
-      <c r="O120" t="inlineStr"/>
-      <c r="P120" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>trig10</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>scaffold</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Apply tangent difference</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>Substitute $$tan\theta_1 = m_1$$ and $$tan\theta_2 = m_2$$ into the tangent difference formula for $$tan(\theta_2 - \theta_1)$$.</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>$$\frac{m_{2}−m_{1}}{1+m_{1}m_{2}}$$</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>algebraic</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>s3</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>h3</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
-      <c r="O121" t="inlineStr"/>
-      <c r="P121" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr"/>
-      <c r="B122" t="inlineStr"/>
-      <c r="C122" t="inlineStr"/>
-      <c r="D122" t="inlineStr"/>
-      <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr"/>
-      <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
-      <c r="O122" t="inlineStr"/>
-      <c r="P122" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>trig11</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>problem</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Investigating a Guy-wire Problem</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr"/>
-      <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr"/>
-      <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr">
-        <is>
-          <t>https://openstax.org/books/precalculus-2e/pages/7-2-sum-and-difference-identities</t>
-        </is>
-      </c>
-      <c r="M123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
-      <c r="O123" t="inlineStr"/>
-      <c r="P123" t="inlineStr"/>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>trig11</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>step</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Find the angle $$α$$ between the two guy-wires attached to a pole at heights 47 feet and 40 feet, both attached to the ground 50 feet from the pole.</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr"/>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>$$\arctan\left(\frac{35}{438}\right)$$</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr"/>
-      <c r="H124" t="inlineStr"/>
-      <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
-      <c r="O124" t="inlineStr"/>
-      <c r="P124" t="inlineStr"/>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>trig11</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>hint</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Identify angles of elevation</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>Consider the angles of elevation that each wire makes with the ground. Let these be $$\theta_R$$ for wire R and $$\theta_S$$ for wire S.</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>h1</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr"/>
-      <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
-      <c r="O125" t="inlineStr"/>
-      <c r="P125" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>trig11</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>scaffold</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Calculate $$tan(\theta_R)$$ and $$tan(\theta_S)$$</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>What are the tangent values for the angles of elevation of wire R (47 ft high) and wire S (40 ft high), given they are both 50 ft from the pole?</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>$$tan(\theta_R) = 47/50, tan(\theta_S) = 40/50$$</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>algebraic</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>s1</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>h1</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
-      <c r="O126" t="inlineStr"/>
-      <c r="P126" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>trig11</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>hint</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Angle between wires</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>The angle $$\alpha$$ between the wires at the ground attachment point is the difference between their angles of elevation.</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr"/>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>h1</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
-      <c r="O127" t="inlineStr"/>
-      <c r="P127" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>trig11</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>scaffold</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Express $$\alpha$$</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>How can you express $$\alpha$$ in terms of $$\theta_R$$ and $$\theta_S$$?</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>$$\alpha = \theta_R - \theta_S$$</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>algebraic</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>s2</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
-      <c r="O128" t="inlineStr"/>
-      <c r="P128" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>trig11</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>hint</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Tangent difference formula</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>Apply the tangent difference identity: $$tan(A - B) = \frac{tan A - tan B}{1 + tan A tan B}$$ to find $$tan(\alpha)$$.</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr"/>
-      <c r="F129" t="inlineStr"/>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>h3</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
-      <c r="O129" t="inlineStr"/>
-      <c r="P129" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>trig11</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>scaffold</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Calculate $$tan(\alpha)$$</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>Substitute the tangent values from Scaffold 1 into the tangent difference formula to find $$tan(\alpha)$$.</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>35/438</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>s3</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>h3</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
-      <c r="L130" t="inlineStr"/>
-      <c r="M130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
-      <c r="O130" t="inlineStr"/>
-      <c r="P130" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
